--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L215"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>שרון יפעת - Fly</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410667&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Keith Urban</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>שרון יפעת - Fly</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>שירז - מאמי איפה עפת</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410666&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Danna</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>שירז - מאמי איפה עפת</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410664&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Armik</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>עידו כנפי - לבכות על כתפך</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410662&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Europe</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>עידו כנפי - לבכות על כתפך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410661&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Foo Fighters</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>יהונתן שתיוי - גיב מי דאט</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410660&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>יהונתן שתיוי - גיב מי דאט</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>איציק מארי - כותב עלייך שיר</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410659&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Muse</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>איציק מארי - כותב עלייך שיר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>אביחי פרץ - משבר</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410656&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Nothing But Thieves</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>אביחי פרץ - משבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>שרון הולצמן לראות אותך הלילה</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9c%d7%a8%d7%90%d7%95%d7%aa-%d7%90%d7%95%d7%aa%d7%9a-%d7%94%d7%9c%d7%99%d7%9c%d7%94/</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-01</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>"לראות אותך הלילה" של שרון הולצמן הוא בלדת רוק אינטימית – כזו שלא נשענת על תחכום צורני אלא על רגש חשוף וישיר. דווקא הפשטות היא חלק מרכזי מהכוח שלה. כבר בשורה הפותחת נוצרת דינמיקה של תלות רגשית חזקה – "רק</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Shaboozey</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>שרון הולצמן לראות אותך הלילה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410665&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-01</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Scorpions</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410663&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-01</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Meghan Trainor</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>אוראל מנצור - האיש ההוא קאבר</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410658&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-01</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Lolo Zouaï</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>אוראל מנצור - האיש ההוא קאבר</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410657&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-01</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bonnie Tyler</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Icona Pop</v>
+        <v>Danna</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Michael Jackson</v>
+        <v>Armik</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>The All-American Rejects</v>
+        <v>Europe</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Ringo Starr</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Demi Lovato</v>
+        <v>Muse</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-01</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-01</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Ella Langley</v>
+        <v>Scorpions</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-01</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-01</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lukas Graham</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-01</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Foo Fighters</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-01</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>RUEL</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-01</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Haiden Henderson</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Conan Gray</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Foo Fighters</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-01</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-01</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bublé</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-01</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Malcolm Todd</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-01</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Sam Feldt</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-01</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Niall Horan</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-01</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-01</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Duran Duran</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Freya Skye</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Danna</v>
+        <v>RUEL</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Cannons</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Beck</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Digster Pop Music</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Beck</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The All-American Rejects</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Armin van Buuren</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Demi Lovato</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Madonna</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Freya Ridings</v>
+        <v>Danna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Celine Dion</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Peter Gabriel</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-01</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Cannons</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware</v>
+        <v>Beck</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>ERNEST</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-01</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dean Lewis</v>
+        <v>Beck</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-01</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kip Moore</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-01</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-01</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Ben Gallaher</v>
+        <v>Madonna</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-01</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Johnny Orlando</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-01</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Tyla</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-01</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-01</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lana Del Rey</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-01</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Loreen</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-01</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bonnie Tyler</v>
+        <v>ERNEST</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-01</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tenille Townes</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-01</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-01</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Danna</v>
+        <v>Bella White</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-01</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>OneRepublic</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-01</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Revivalists</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-01</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>James Smith</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-01</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Holly Humberstone</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-01</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ava Max</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-01</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>John Summit</v>
+        <v>Tyla</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-01</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Ava Max</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-01</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Danna</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-01</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Conan Gray</v>
+        <v>Loreen</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-01</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>TemplesOfficial</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-01</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-01</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>bleachers</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-01</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Danna</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-01</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>LANY</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-01</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-01</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>James Smith</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-01</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-01</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Ava Max</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-01</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>florencemachine</v>
+        <v>John Summit</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-01</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Scorpions</v>
+        <v>Ava Max</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-01</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Holly Humberstone</v>
+        <v>Danna</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-01</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>HAUSER</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-01</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Holly Humberstone</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-01</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Laufey</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-01</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Mae Muller</v>
+        <v>bleachers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Zara Larsson</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shape of a Woman</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:29</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Lady Gaga</v>
+        <v>LANY</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Bring Your Love</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>CONFESSIONS II</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:36</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Madonna</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Horses and Divorces</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Middle of Nowhere</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:43</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Staying Still</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>4:28</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:07</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Alex Warren</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>MUTT</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>MUTT - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>1:59</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>NAV</v>
+        <v>florencemachine</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>MUTT - NAV</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Victory</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:27</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Madeon</v>
+        <v>Scorpions</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Lioness</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:32</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>Maya Hawke</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>IT'S OK</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>IT'S OK - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:19</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Bryson Tiller</v>
+        <v>HAUSER</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Promise?</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Promise? - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>3:12</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>Bella Kay</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Cool Buzz</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Be Sweet To Me</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>2:32</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>Violet Grohl</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Material Lover</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>2:58</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>BROWN</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G115" t="str">
-        <v>4:26</v>
+        <v>2:50</v>
       </c>
       <c r="H115" t="str">
-        <v>Chris Brown</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L115" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Echo</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G116" t="str">
-        <v>2:15</v>
+        <v>3:29</v>
       </c>
       <c r="H116" t="str">
-        <v>Daddy Yankee</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L116" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Cry Baby</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G117" t="str">
-        <v>3:52</v>
+        <v>3:36</v>
       </c>
       <c r="H117" t="str">
-        <v>Vince Staples</v>
+        <v>Madonna</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L117" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Ricky Bobby</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>CORSA</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G118" t="str">
-        <v>2:55</v>
+        <v>2:43</v>
       </c>
       <c r="H118" t="str">
-        <v>Eladio Carrión</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L118" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Staying Still</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G119" t="str">
-        <v>5:35</v>
+        <v>4:28</v>
       </c>
       <c r="H119" t="str">
-        <v>Maisak</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L119" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Don't Worry Baby</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:27</v>
+        <v>3:07</v>
       </c>
       <c r="H120" t="str">
-        <v>Dom Dolla</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L120" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>BITCH</v>
+        <v>MUTT</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>BITCH</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:42</v>
+        <v>1:59</v>
       </c>
       <c r="H121" t="str">
-        <v>Lizzo</v>
+        <v>NAV</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L121" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Just Wanna Cry</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>Victory</v>
       </c>
       <c r="G122" t="str">
-        <v>2:27</v>
+        <v>3:27</v>
       </c>
       <c r="H122" t="str">
-        <v>Meghan Trainor</v>
+        <v>Madeon</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L122" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Carry the Weight</v>
+        <v>Lioness</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G123" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H123" t="str">
-        <v>Halsey</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L123" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PROSTITUTE</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:44</v>
+        <v>2:19</v>
       </c>
       <c r="H124" t="str">
-        <v>Labrinth</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L124" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>i'm not joking</v>
+        <v>Promise?</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:54</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>Bleachers</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L125" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Ruca</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>MUDA</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G126" t="str">
-        <v>3:01</v>
+        <v>2:32</v>
       </c>
       <c r="H126" t="str">
-        <v>Carín León</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L126" t="str">
-        <v>Ruca - Carín León</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Make You Fight</v>
+        <v>Material Lover</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Make You Fight - Single</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G127" t="str">
-        <v>2:55</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Chris Lake</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L127" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>#N0rth4evr</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>BROWN</v>
       </c>
       <c r="G128" t="str">
-        <v>1:43</v>
+        <v>4:26</v>
       </c>
       <c r="H128" t="str">
-        <v>North West</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L128" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOY IN RED</v>
+        <v>Echo</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:09</v>
+        <v>2:15</v>
       </c>
       <c r="H129" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L129" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>EA EA EA</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G130" t="str">
-        <v>2:42</v>
+        <v>3:52</v>
       </c>
       <c r="H130" t="str">
-        <v>Clave Especial</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L130" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Just A Man</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Just A Man - Single</v>
+        <v>CORSA</v>
       </c>
       <c r="G131" t="str">
-        <v>2:19</v>
+        <v>2:55</v>
       </c>
       <c r="H131" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L131" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>The Observer</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>5:35</v>
       </c>
       <c r="H132" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Maisak</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L132" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Heroine</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heroine - Single</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:35</v>
+        <v>3:27</v>
       </c>
       <c r="H133" t="str">
-        <v>Maroon 5</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L133" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Do Me Right</v>
+        <v>BITCH</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FANTASYLAND</v>
+        <v>BITCH</v>
       </c>
       <c r="G134" t="str">
-        <v>4:10</v>
+        <v>2:42</v>
       </c>
       <c r="H134" t="str">
-        <v>MR. FANTASY</v>
+        <v>Lizzo</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L134" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>It's Me</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G135" t="str">
-        <v>2:18</v>
+        <v>2:27</v>
       </c>
       <c r="H135" t="str">
-        <v>ILLIT</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L135" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>the precipice</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G136" t="str">
-        <v>3:52</v>
+        <v>3:09</v>
       </c>
       <c r="H136" t="str">
-        <v>Jessie Mazin</v>
+        <v>Halsey</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L136" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Hello Lonesome</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G137" t="str">
-        <v>2:58</v>
+        <v>2:44</v>
       </c>
       <c r="H137" t="str">
-        <v>Cody Johnson</v>
+        <v>Labrinth</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L137" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G138" t="str">
-        <v>2:21</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>BUNT.</v>
+        <v>Bleachers</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L138" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>Ruca</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>MUDA</v>
       </c>
       <c r="G139" t="str">
-        <v>5:54</v>
+        <v>3:01</v>
       </c>
       <c r="H139" t="str">
-        <v>Ludwig Göransson</v>
+        <v>Carín León</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:49</v>
+        <v>2:55</v>
       </c>
       <c r="H140" t="str">
-        <v>Robyn</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Bring That Body</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bring That Body - Single</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G141" t="str">
-        <v>3:34</v>
+        <v>1:43</v>
       </c>
       <c r="H141" t="str">
-        <v>The-Dream</v>
+        <v>North West</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L141" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>STAR</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>STAR</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G142" t="str">
-        <v>2:49</v>
+        <v>3:09</v>
       </c>
       <c r="H142" t="str">
-        <v>Tombochio</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L142" t="str">
-        <v>STAR - Tombochio</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>What’s A Little Rain</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Deep Blue</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>3:37</v>
+        <v>2:42</v>
       </c>
       <c r="H143" t="str">
-        <v>ERNEST</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L143" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Evergreen</v>
+        <v>Just A Man</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Victory Garden</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:41</v>
+        <v>2:19</v>
       </c>
       <c r="H144" t="str">
-        <v>Young the Giant</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L144" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>She Does It Right</v>
+        <v>The Observer</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Peaches!</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G145" t="str">
-        <v>3:43</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>The Black Keys</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L145" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Punching the Flowers</v>
+        <v>Heroine</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>I Built You A Tower</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:11</v>
+        <v>2:35</v>
       </c>
       <c r="H146" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L146" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>How Did You Know</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G147" t="str">
-        <v>3:16</v>
+        <v>4:10</v>
       </c>
       <c r="H147" t="str">
-        <v>Jon Pardi</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L147" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Summer Breeze</v>
+        <v>It's Me</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>flow state</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>4:00</v>
+        <v>2:18</v>
       </c>
       <c r="H148" t="str">
-        <v>Keith Urban</v>
+        <v>ILLIT</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L148" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Sound of a Woman</v>
+        <v>the precipice</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Sound of a Woman</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>4:27</v>
+        <v>3:52</v>
       </c>
       <c r="H149" t="str">
-        <v>Rita Wilson</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L149" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>My Life</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>BERNARR.</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G150" t="str">
-        <v>3:31</v>
+        <v>2:58</v>
       </c>
       <c r="H150" t="str">
-        <v>Durand Bernarr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L150" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ribcage</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ribcage - Single</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:00</v>
+        <v>2:21</v>
       </c>
       <c r="H151" t="str">
-        <v>Bella Poarch</v>
+        <v>BUNT.</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L151" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>i loved you then</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:42</v>
+        <v>5:54</v>
       </c>
       <c r="H152" t="str">
-        <v>Alana Springsteen</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L152" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>I'll Let You Finish</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Fire From The Hip</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:54</v>
+        <v>2:49</v>
       </c>
       <c r="H153" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Robyn</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L153" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>It Gets Me Through</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:53</v>
+        <v>3:34</v>
       </c>
       <c r="H154" t="str">
-        <v>Laura Marano</v>
+        <v>The-Dream</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L154" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>The Author</v>
+        <v>STAR</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Author - Single</v>
+        <v>STAR</v>
       </c>
       <c r="G155" t="str">
-        <v>4:36</v>
+        <v>2:49</v>
       </c>
       <c r="H155" t="str">
-        <v>Brandon Lake</v>
+        <v>Tombochio</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L155" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>3:37</v>
       </c>
       <c r="H156" t="str">
-        <v>Trousdale</v>
+        <v>ERNEST</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L156" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>RUIN</v>
+        <v>Evergreen</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>ADDENDUM</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G157" t="str">
-        <v>3:23</v>
+        <v>3:41</v>
       </c>
       <c r="H157" t="str">
-        <v>HEALTH</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L157" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>I Know I Know</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>I Know I Know - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G158" t="str">
-        <v>2:39</v>
+        <v>3:43</v>
       </c>
       <c r="H158" t="str">
-        <v>STELLA LEFTY</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L158" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Drive All Night</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Drive All Night - Single</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G159" t="str">
-        <v>2:50</v>
+        <v>3:11</v>
       </c>
       <c r="H159" t="str">
-        <v>Wyatt Flores</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L159" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G160" t="str">
-        <v>3:41</v>
+        <v>3:16</v>
       </c>
       <c r="H160" t="str">
-        <v>Jessie Reyez</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L160" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Boys In Blue</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Emotional Junglist</v>
+        <v>flow state</v>
       </c>
       <c r="G161" t="str">
-        <v>2:33</v>
+        <v>4:00</v>
       </c>
       <c r="H161" t="str">
-        <v>Nia Archives</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L161" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Salma Hayek</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G162" t="str">
-        <v>3:43</v>
+        <v>4:27</v>
       </c>
       <c r="H162" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L162" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Stubborn Mouth</v>
+        <v>My Life</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G163" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H163" t="str">
-        <v>Girl Tones</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L163" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Hallucination</v>
+        <v>Ribcage</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:22</v>
+        <v>3:00</v>
       </c>
       <c r="H164" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L164" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>In Da Jungle</v>
+        <v>i loved you then</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G165" t="str">
-        <v>2:44</v>
+        <v>3:42</v>
       </c>
       <c r="H165" t="str">
-        <v>BLOND:ISH</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L165" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Fall Short</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Fall Short - Single</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G166" t="str">
-        <v>2:44</v>
+        <v>3:54</v>
       </c>
       <c r="H166" t="str">
-        <v>nyan</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L166" t="str">
-        <v>Fall Short - nyan</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>FENIAN</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H167" t="str">
-        <v>Kneecap</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L167" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>1989</v>
+        <v>The Author</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>1989 - Single</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:05</v>
+        <v>4:36</v>
       </c>
       <c r="H168" t="str">
-        <v>Nightly</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L168" t="str">
-        <v>1989 - Nightly</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>no more regrets</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>no more regrets - Single</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:58</v>
+        <v>3:44</v>
       </c>
       <c r="H169" t="str">
-        <v>almost monday</v>
+        <v>Trousdale</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L169" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drum Machine</v>
+        <v>RUIN</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Sweat</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G170" t="str">
-        <v>3:16</v>
+        <v>3:23</v>
       </c>
       <c r="H170" t="str">
-        <v>Melanie C</v>
+        <v>HEALTH</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L170" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>I'm Perfect</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H171" t="str">
-        <v>Olivia O'Brien</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L171" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>5:05</v>
+        <v>2:50</v>
       </c>
       <c r="H172" t="str">
-        <v>Anish Kumar</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L172" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Bitch You Weird</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:27</v>
+        <v>3:41</v>
       </c>
       <c r="H173" t="str">
-        <v>Real Boston Richey</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L173" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Blackbird Rising</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>24</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G174" t="str">
-        <v>2:24</v>
+        <v>2:33</v>
       </c>
       <c r="H174" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L174" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>usher in the spirit</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:00</v>
+        <v>3:43</v>
       </c>
       <c r="H175" t="str">
-        <v>Aaron Cole</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L175" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Moonlight</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Moonlight - Single</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H176" t="str">
-        <v>Chelsea Plank</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L176" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Hallucination</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G177" t="str">
-        <v>2:17</v>
+        <v>3:22</v>
       </c>
       <c r="H177" t="str">
-        <v>Becky Hill</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Closure</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Closure - Single</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:27</v>
+        <v>2:44</v>
       </c>
       <c r="H178" t="str">
-        <v>D.O.D</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L178" t="str">
-        <v>Closure - D.O.D</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>HOTS 4 U</v>
+        <v>Fall Short</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H179" t="str">
-        <v>Chris Lorenzo</v>
+        <v>nyan</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L179" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G180" t="str">
-        <v>2:20</v>
+        <v>3:34</v>
       </c>
       <c r="H180" t="str">
-        <v>ARIA VEGA</v>
+        <v>Kneecap</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The Coin Toss</v>
+        <v>1989</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H181" t="str">
-        <v>Curren$y</v>
+        <v>Nightly</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L181" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>no more regrets</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:25</v>
+        <v>2:58</v>
       </c>
       <c r="H182" t="str">
-        <v>Chxrry</v>
+        <v>almost monday</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L182" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Perfect For Me</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G183" t="str">
-        <v>3:02</v>
+        <v>3:16</v>
       </c>
       <c r="H183" t="str">
-        <v>Jamal Roberts</v>
+        <v>Melanie C</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L183" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>So…</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>So… - Single</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:16</v>
+        <v>2:36</v>
       </c>
       <c r="H184" t="str">
-        <v>Ama</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L184" t="str">
-        <v>So… - Ama</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>PASE Y PASE</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>3:01</v>
+        <v>5:05</v>
       </c>
       <c r="H185" t="str">
-        <v>Tito Double P</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L185" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:13</v>
+        <v>2:27</v>
       </c>
       <c r="H186" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L186" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Aljahalat</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Aljahalat - Single</v>
+        <v>24</v>
       </c>
       <c r="G187" t="str">
-        <v>6:12</v>
+        <v>2:24</v>
       </c>
       <c r="H187" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L187" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Puleza</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>People of the Moon</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:47</v>
+        <v>3:00</v>
       </c>
       <c r="H188" t="str">
-        <v>Nu Genea</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L188" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Bastards</v>
+        <v>Moonlight</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Bunny - EP</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:56</v>
+        <v>3:23</v>
       </c>
       <c r="H189" t="str">
-        <v>People I’ve Met</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L189" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Crutch</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Crutch - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:31</v>
+        <v>2:17</v>
       </c>
       <c r="H190" t="str">
-        <v>Love Spells</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L190" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Just A Man</v>
+        <v>Closure</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Just A Man - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:38</v>
+        <v>2:27</v>
       </c>
       <c r="H191" t="str">
-        <v>MOIO</v>
+        <v>D.O.D</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L191" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Take Care Of You</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:51</v>
+        <v>3:34</v>
       </c>
       <c r="H192" t="str">
-        <v>Alina Baraz</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L192" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Love You More</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Love You More - Single</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:48</v>
+        <v>2:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Rudimental</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L193" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Construct</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>ONE</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G194" t="str">
-        <v>3:57</v>
+        <v>2:46</v>
       </c>
       <c r="H194" t="str">
-        <v>Sevendust</v>
+        <v>Curren$y</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L194" t="str">
-        <v>Construct - Sevendust</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>As Above So Below</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Into Oblivion</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:54</v>
+        <v>3:25</v>
       </c>
       <c r="H195" t="str">
-        <v>Venom</v>
+        <v>Chxrry</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L195" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Revenant</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>A Stranger To You</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:31</v>
+        <v>3:02</v>
       </c>
       <c r="H196" t="str">
-        <v>Loathe</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L196" t="str">
-        <v>Revenant - Loathe</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>So…</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>4:56</v>
+        <v>3:16</v>
       </c>
       <c r="H197" t="str">
-        <v>Bear McCreary</v>
+        <v>Ama</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Power 4</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Power 4 - Single</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>1:40</v>
+        <v>3:01</v>
       </c>
       <c r="H198" t="str">
-        <v>slayr</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L198" t="str">
-        <v>Power 4 - slayr</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Too Easy</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Too Easy - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G199" t="str">
-        <v>4:14</v>
+        <v>4:13</v>
       </c>
       <c r="H199" t="str">
-        <v>tig3r lewis</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L199" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>If You Want It</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>If You Want It - Single</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:56</v>
+        <v>6:12</v>
       </c>
       <c r="H200" t="str">
-        <v>ALAC</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L200" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Shoplifting</v>
+        <v>Puleza</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-01</v>
@@ -8013,68 +8013,562 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Theft World</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G201" t="str">
-        <v>3:02</v>
+        <v>3:47</v>
       </c>
       <c r="H201" t="str">
-        <v>Lip Critic</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L201" t="str">
-        <v>Shoplifting - Lip Critic</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Bastards</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Bunny - EP</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2:56</v>
+      </c>
+      <c r="H202" t="str">
+        <v>People I’ve Met</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Bastards - People I’ve Met</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Crutch</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Crutch - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:31</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Love Spells</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Crutch - Love Spells</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Just A Man</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Just A Man - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H204" t="str">
+        <v>MOIO</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Just A Man - MOIO</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Take Care Of You</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Take Care Of You - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Alina Baraz</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Take Care Of You - Alina Baraz</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Love You More</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Love You More - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:48</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Rudimental</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Love You More - Rudimental</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Construct</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>ONE</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Sevendust</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Construct - Sevendust</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>As Above So Below</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Into Oblivion</v>
+      </c>
+      <c r="G208" t="str">
+        <v>4:54</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Venom</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+      </c>
+      <c r="L208" t="str">
+        <v>As Above So Below - Venom</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Revenant</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>A Stranger To You</v>
+      </c>
+      <c r="G209" t="str">
+        <v>3:31</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Loathe</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Revenant - Loathe</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>4:56</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Bear McCreary</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Power 4</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Power 4 - Single</v>
+      </c>
+      <c r="G211" t="str">
+        <v>1:40</v>
+      </c>
+      <c r="H211" t="str">
+        <v>slayr</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Power 4 - slayr</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Too Easy</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Too Easy - Single</v>
+      </c>
+      <c r="G212" t="str">
+        <v>4:14</v>
+      </c>
+      <c r="H212" t="str">
+        <v>tig3r lewis</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Too Easy - tig3r lewis</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>If You Want It</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>If You Want It - Single</v>
+      </c>
+      <c r="G213" t="str">
+        <v>3:56</v>
+      </c>
+      <c r="H213" t="str">
+        <v>ALAC</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+      </c>
+      <c r="L213" t="str">
+        <v>If You Want It - ALAC</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Shoplifting</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>Theft World</v>
+      </c>
+      <c r="G214" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Lip Critic</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Shoplifting - Lip Critic</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
         <v>Endlessly (feat. BEA1991)</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D215" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
         <v>Fold</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G215" t="str">
         <v>5:57</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H215" t="str">
         <v>Jump Source</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
         <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K215" t="str">
         <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L215" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L215"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L215"/>
+  <dimension ref="A1:L207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון יפעת - Fly</v>
+        <v>צוף מימון &amp; יקיר - שקוף</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410667&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410671&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון יפעת - Fly</v>
+        <v>צוף מימון &amp; יקיר - שקוף</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שירז - מאמי איפה עפת</v>
+        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410666&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410670&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שירז - מאמי איפה עפת</v>
+        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
+        <v>אלשי שמואל - נכתב לנו מזמן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410664&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410669&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-01</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
+        <v>אלשי שמואל - נכתב לנו מזמן</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עידו כנפי - לבכות על כתפך</v>
+        <v>איציק מארי - עוף מדבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410662&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410668&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-01</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עידו כנפי - לבכות על כתפך</v>
+        <v>איציק מארי - עוף מדבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
+        <v>סקינרד You got this</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410661&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>https://yosmusic.com/%d7%a1%d7%a7%d7%99%d7%a0%d7%a8%d7%93-you-got-this/</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-01</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>הרכב הרגאיי-מטאל מניופורט, סקינרד Skindred, מוכרים כלהקה חיה סוחפת במיוחד, אבל האלבום “Smile” מ-2023 שינה את כללי המשחק. הוא הגיע למקום השני במצעדים בבריטניה, הוביל להופעת סולד אאוט באולם וומבלי ארנה, ולזכייה גאה בפרס להקת האלטרנטיב הטובה ביותר בטקס פרסי</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
+        <v>סקינרד You got this</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יהונתן שתיוי - גיב מי דאט</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410660&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Keith Urban</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יהונתן שתיוי - גיב מי דאט</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>איציק מארי - כותב עלייך שיר</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410659&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>איציק מארי - כותב עלייך שיר</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אביחי פרץ - משבר</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410656&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Armik</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אביחי פרץ - משבר</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>שרון הולצמן לראות אותך הלילה</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9c%d7%a8%d7%90%d7%95%d7%aa-%d7%90%d7%95%d7%aa%d7%9a-%d7%94%d7%9c%d7%99%d7%9c%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-01</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>"לראות אותך הלילה" של שרון הולצמן הוא בלדת רוק אינטימית – כזו שלא נשענת על תחכום צורני אלא על רגש חשוף וישיר. דווקא הפשטות היא חלק מרכזי מהכוח שלה. כבר בשורה הפותחת נוצרת דינמיקה של תלות רגשית חזקה – "רק</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>שרון הולצמן לראות אותך הלילה</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-01</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410665&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-01</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Foo Fighters</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-05-01</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410663&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-01</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אוראל מנצור - האיש ההוא קאבר</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-05-01</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410658&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-01</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Muse</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אוראל מנצור - האיש ההוא קאבר</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-05-01</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410657&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-01</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Keith Urban</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Danna</v>
+        <v>Scorpions</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Armik</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Europe</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Foo Fighters</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Muse</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-01</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Shaboozey</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-01</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Scorpions</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-01</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Meghan Trainor</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-01</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-01</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-01</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-01</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Icona Pop</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Michael Jackson</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>The All-American Rejects</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-01</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-01</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>RUEL</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-01</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-01</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Dean Lewis</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-01</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Matt Hansen</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-01</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Ella Langley</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-01</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Meghan Trainor</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-01</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Lukas Graham</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-01</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Foo Fighters</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-01</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>RUEL</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-01</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Haiden Henderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Conan Gray</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Foo Fighters</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Ringo Starr</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Michael Bublé</v>
+        <v>Danna</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Malcolm Todd</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Sam Feldt</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Niall Horan</v>
+        <v>Cannons</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Beck</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Duran Duran</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Freya Skye</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Danna</v>
+        <v>Beck</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Purple Disco Machine</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-01</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Cannons</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Beck</v>
+        <v>Madonna</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-01</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Digster Pop Music</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Beck</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-01</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>The All-American Rejects</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-01</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Demi Lovato</v>
+        <v>ERNEST</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-01</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Madonna</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-01</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Freya Ridings</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Celine Dion</v>
+        <v>Bella White</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-01</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Peter Gabriel</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-01</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-01</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Jessie Ware</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-01</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-01</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>ERNEST</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-01</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Tyla</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-01</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Dean Lewis</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-01</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Bella White</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-01</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Kip Moore</v>
+        <v>Loreen</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-01</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-01</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Ben Gallaher</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-01</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-01</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Johnny Orlando</v>
+        <v>Danna</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-01</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Tyla</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-01</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Lewis Capaldi</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-01</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Lana Del Rey</v>
+        <v>James Smith</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-01</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Loreen</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-01</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Ava Max</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-01</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Tenille Townes</v>
+        <v>John Summit</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-01</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Ava Max</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-01</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-01</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>OneRepublic</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-01</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>The Revivalists</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-01</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>James Smith</v>
+        <v>Laufey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-01</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Holly Humberstone</v>
+        <v>bleachers</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-01</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Ava Max</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-01</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>John Summit</v>
+        <v>LANY</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-01</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Ava Max</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-01</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Danna</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-01</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Conan Gray</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-01</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>TemplesOfficial</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-01</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Laufey</v>
+        <v>florencemachine</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-01</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>bleachers</v>
+        <v>Scorpions</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B102" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-01</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B103" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-01</v>
@@ -4295,7 +4295,7 @@
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>LANY</v>
+        <v>HAUSER</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B104" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-01</v>
@@ -4333,7 +4333,7 @@
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,18 +4345,18 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-01</v>
@@ -4365,13 +4365,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
         <v/>
       </c>
       <c r="H105" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,18 +4383,18 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-01</v>
@@ -4403,13 +4403,13 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G106" t="str">
         <v/>
       </c>
       <c r="H106" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4421,18 +4421,18 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H107" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L107" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>3:29</v>
       </c>
       <c r="H108" t="str">
-        <v>florencemachine</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L108" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>3:36</v>
       </c>
       <c r="H109" t="str">
-        <v>Scorpions</v>
+        <v>Madonna</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L109" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>Holly Humberstone</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L110" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Staying Still</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>4:28</v>
       </c>
       <c r="H111" t="str">
-        <v>HAUSER</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L111" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B112" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>2 weeks ago</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>3:07</v>
       </c>
       <c r="H112" t="str">
-        <v>Holly Humberstone</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L112" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>MUTT</v>
       </c>
       <c r="B113" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>2 weeks ago</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>1:59</v>
       </c>
       <c r="H113" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>NAV</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L113" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B114" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>3 weeks ago</v>
+        <v>Victory</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>3:27</v>
       </c>
       <c r="H114" t="str">
-        <v>Mae Muller</v>
+        <v>Madeon</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L114" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Lioness</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G115" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H115" t="str">
-        <v>Zara Larsson</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L115" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Shape of a Woman</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:29</v>
+        <v>2:19</v>
       </c>
       <c r="H116" t="str">
-        <v>Lady Gaga</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L116" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Bring Your Love</v>
+        <v>Promise?</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>CONFESSIONS II</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:36</v>
+        <v>3:12</v>
       </c>
       <c r="H117" t="str">
-        <v>Madonna</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L117" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Horses and Divorces</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G118" t="str">
-        <v>2:43</v>
+        <v>2:32</v>
       </c>
       <c r="H118" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L118" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Staying Still</v>
+        <v>Material Lover</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G119" t="str">
-        <v>4:28</v>
+        <v>2:58</v>
       </c>
       <c r="H119" t="str">
-        <v>Noah Kahan</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L119" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>BROWN</v>
       </c>
       <c r="G120" t="str">
-        <v>3:07</v>
+        <v>4:26</v>
       </c>
       <c r="H120" t="str">
-        <v>Alex Warren</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L120" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>MUTT</v>
+        <v>Echo</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>MUTT - Single</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>1:59</v>
+        <v>2:15</v>
       </c>
       <c r="H121" t="str">
-        <v>NAV</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L121" t="str">
-        <v>MUTT - NAV</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Victory</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G122" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H122" t="str">
-        <v>Madeon</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L122" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Lioness</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>CORSA</v>
       </c>
       <c r="G123" t="str">
-        <v>3:32</v>
+        <v>2:55</v>
       </c>
       <c r="H123" t="str">
-        <v>Maya Hawke</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L123" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>IT'S OK</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:19</v>
+        <v>5:35</v>
       </c>
       <c r="H124" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maisak</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L124" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Promise?</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Promise? - Single</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>3:27</v>
       </c>
       <c r="H125" t="str">
-        <v>Bella Kay</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L125" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Cool Buzz</v>
+        <v>BITCH</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Be Sweet To Me</v>
+        <v>BITCH</v>
       </c>
       <c r="G126" t="str">
-        <v>2:32</v>
+        <v>2:42</v>
       </c>
       <c r="H126" t="str">
-        <v>Violet Grohl</v>
+        <v>Lizzo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L126" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Material Lover</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:27</v>
       </c>
       <c r="H127" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L127" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>BROWN</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G128" t="str">
-        <v>4:26</v>
+        <v>3:09</v>
       </c>
       <c r="H128" t="str">
-        <v>Chris Brown</v>
+        <v>Halsey</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L128" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Echo</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G129" t="str">
-        <v>2:15</v>
+        <v>2:44</v>
       </c>
       <c r="H129" t="str">
-        <v>Daddy Yankee</v>
+        <v>Labrinth</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L129" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Cry Baby</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G130" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H130" t="str">
-        <v>Vince Staples</v>
+        <v>Bleachers</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L130" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Ricky Bobby</v>
+        <v>Ruca</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>CORSA</v>
+        <v>MUDA</v>
       </c>
       <c r="G131" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H131" t="str">
-        <v>Eladio Carrión</v>
+        <v>Carín León</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L131" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>5:35</v>
+        <v>2:55</v>
       </c>
       <c r="H132" t="str">
-        <v>Maisak</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L132" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Don't Worry Baby</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:27</v>
+        <v>1:43</v>
       </c>
       <c r="H133" t="str">
-        <v>Dom Dolla</v>
+        <v>North West</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L133" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>BITCH</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>BITCH</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G134" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H134" t="str">
-        <v>Lizzo</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L134" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Just Wanna Cry</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G135" t="str">
-        <v>2:27</v>
+        <v>2:42</v>
       </c>
       <c r="H135" t="str">
-        <v>Meghan Trainor</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L135" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Carry the Weight</v>
+        <v>Just A Man</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:09</v>
+        <v>2:19</v>
       </c>
       <c r="H136" t="str">
-        <v>Halsey</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L136" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>PROSTITUTE</v>
+        <v>The Observer</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G137" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H137" t="str">
-        <v>Labrinth</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L137" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>i'm not joking</v>
+        <v>Heroine</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:54</v>
+        <v>2:35</v>
       </c>
       <c r="H138" t="str">
-        <v>Bleachers</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L138" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ruca</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>MUDA</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G139" t="str">
-        <v>3:01</v>
+        <v>4:10</v>
       </c>
       <c r="H139" t="str">
-        <v>Carín León</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L139" t="str">
-        <v>Ruca - Carín León</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Make You Fight</v>
+        <v>It's Me</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Make You Fight - Single</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>2:55</v>
+        <v>2:18</v>
       </c>
       <c r="H140" t="str">
-        <v>Chris Lake</v>
+        <v>ILLIT</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L140" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>#N0rth4evr</v>
+        <v>the precipice</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G141" t="str">
-        <v>1:43</v>
+        <v>3:52</v>
       </c>
       <c r="H141" t="str">
-        <v>North West</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L141" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>BOY IN RED</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G142" t="str">
-        <v>3:09</v>
+        <v>2:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L142" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>EA EA EA</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:42</v>
+        <v>2:21</v>
       </c>
       <c r="H143" t="str">
-        <v>Clave Especial</v>
+        <v>BUNT.</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L143" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Just A Man</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Just A Man - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:19</v>
+        <v>5:54</v>
       </c>
       <c r="H144" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L144" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>The Observer</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>2:49</v>
       </c>
       <c r="H145" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Robyn</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L145" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Heroine</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Heroine - Single</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Maroon 5</v>
+        <v>The-Dream</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L146" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Do Me Right</v>
+        <v>STAR</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>FANTASYLAND</v>
+        <v>STAR</v>
       </c>
       <c r="G147" t="str">
-        <v>4:10</v>
+        <v>2:49</v>
       </c>
       <c r="H147" t="str">
-        <v>MR. FANTASY</v>
+        <v>Tombochio</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L147" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>It's Me</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G148" t="str">
-        <v>2:18</v>
+        <v>3:37</v>
       </c>
       <c r="H148" t="str">
-        <v>ILLIT</v>
+        <v>ERNEST</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L148" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>the precipice</v>
+        <v>Evergreen</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G149" t="str">
-        <v>3:52</v>
+        <v>3:41</v>
       </c>
       <c r="H149" t="str">
-        <v>Jessie Mazin</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L149" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Hello Lonesome</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Peaches!</v>
       </c>
       <c r="G150" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H150" t="str">
-        <v>Cody Johnson</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L150" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G151" t="str">
-        <v>2:21</v>
+        <v>3:11</v>
       </c>
       <c r="H151" t="str">
-        <v>BUNT.</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L151" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G152" t="str">
-        <v>5:54</v>
+        <v>3:16</v>
       </c>
       <c r="H152" t="str">
-        <v>Ludwig Göransson</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L152" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>flow state</v>
       </c>
       <c r="G153" t="str">
-        <v>2:49</v>
+        <v>4:00</v>
       </c>
       <c r="H153" t="str">
-        <v>Robyn</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L153" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Bring That Body</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Bring That Body - Single</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G154" t="str">
-        <v>3:34</v>
+        <v>4:27</v>
       </c>
       <c r="H154" t="str">
-        <v>The-Dream</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L154" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>STAR</v>
+        <v>My Life</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>STAR</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G155" t="str">
-        <v>2:49</v>
+        <v>3:31</v>
       </c>
       <c r="H155" t="str">
-        <v>Tombochio</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L155" t="str">
-        <v>STAR - Tombochio</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>What’s A Little Rain</v>
+        <v>Ribcage</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Deep Blue</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:37</v>
+        <v>3:00</v>
       </c>
       <c r="H156" t="str">
-        <v>ERNEST</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L156" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Evergreen</v>
+        <v>i loved you then</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Victory Garden</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G157" t="str">
-        <v>3:41</v>
+        <v>3:42</v>
       </c>
       <c r="H157" t="str">
-        <v>Young the Giant</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L157" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>She Does It Right</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Peaches!</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G158" t="str">
-        <v>3:43</v>
+        <v>3:54</v>
       </c>
       <c r="H158" t="str">
-        <v>The Black Keys</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L158" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Punching the Flowers</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>I Built You A Tower</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:11</v>
+        <v>2:53</v>
       </c>
       <c r="H159" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L159" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>How Did You Know</v>
+        <v>The Author</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:16</v>
+        <v>4:36</v>
       </c>
       <c r="H160" t="str">
-        <v>Jon Pardi</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L160" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Summer Breeze</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>flow state</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:00</v>
+        <v>3:44</v>
       </c>
       <c r="H161" t="str">
-        <v>Keith Urban</v>
+        <v>Trousdale</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L161" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Sound of a Woman</v>
+        <v>RUIN</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Sound of a Woman</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G162" t="str">
-        <v>4:27</v>
+        <v>3:23</v>
       </c>
       <c r="H162" t="str">
-        <v>Rita Wilson</v>
+        <v>HEALTH</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L162" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>My Life</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>BERNARR.</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:31</v>
+        <v>2:39</v>
       </c>
       <c r="H163" t="str">
-        <v>Durand Bernarr</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L163" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Ribcage</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Ribcage - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:00</v>
+        <v>2:50</v>
       </c>
       <c r="H164" t="str">
-        <v>Bella Poarch</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L164" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>i loved you then</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:42</v>
+        <v>3:41</v>
       </c>
       <c r="H165" t="str">
-        <v>Alana Springsteen</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L165" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I'll Let You Finish</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Fire From The Hip</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G166" t="str">
-        <v>3:54</v>
+        <v>2:33</v>
       </c>
       <c r="H166" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L166" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>It Gets Me Through</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H167" t="str">
-        <v>Laura Marano</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L167" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Author</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Author - Single</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:36</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Brandon Lake</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L168" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>Hallucination</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>Trousdale</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L169" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>RUIN</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>ADDENDUM</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:23</v>
+        <v>2:44</v>
       </c>
       <c r="H170" t="str">
-        <v>HEALTH</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L170" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>I Know I Know</v>
+        <v>Fall Short</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Know I Know - Single</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:39</v>
+        <v>2:44</v>
       </c>
       <c r="H171" t="str">
-        <v>STELLA LEFTY</v>
+        <v>nyan</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L171" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drive All Night</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Drive All Night - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G172" t="str">
-        <v>2:50</v>
+        <v>3:34</v>
       </c>
       <c r="H172" t="str">
-        <v>Wyatt Flores</v>
+        <v>Kneecap</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L172" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>1989</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:41</v>
+        <v>3:05</v>
       </c>
       <c r="H173" t="str">
-        <v>Jessie Reyez</v>
+        <v>Nightly</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L173" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Boys In Blue</v>
+        <v>no more regrets</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Emotional Junglist</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:33</v>
+        <v>2:58</v>
       </c>
       <c r="H174" t="str">
-        <v>Nia Archives</v>
+        <v>almost monday</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L174" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Salma Hayek</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G175" t="str">
-        <v>3:43</v>
+        <v>3:16</v>
       </c>
       <c r="H175" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Melanie C</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L175" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Stubborn Mouth</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:02</v>
+        <v>2:36</v>
       </c>
       <c r="H176" t="str">
-        <v>Girl Tones</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L176" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Hallucination</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G177" t="str">
-        <v>3:22</v>
+        <v>5:05</v>
       </c>
       <c r="H177" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L177" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>In Da Jungle</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:44</v>
+        <v>2:27</v>
       </c>
       <c r="H178" t="str">
-        <v>BLOND:ISH</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L178" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fall Short</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Fall Short - Single</v>
+        <v>24</v>
       </c>
       <c r="G179" t="str">
-        <v>2:44</v>
+        <v>2:24</v>
       </c>
       <c r="H179" t="str">
-        <v>nyan</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L179" t="str">
-        <v>Fall Short - nyan</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>FENIAN</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H180" t="str">
-        <v>Kneecap</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L180" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>1989</v>
+        <v>Moonlight</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>1989 - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:05</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Nightly</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L181" t="str">
-        <v>1989 - Nightly</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>no more regrets</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>no more regrets - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:58</v>
+        <v>2:17</v>
       </c>
       <c r="H182" t="str">
-        <v>almost monday</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L182" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Drum Machine</v>
+        <v>Closure</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Sweat</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:16</v>
+        <v>2:27</v>
       </c>
       <c r="H183" t="str">
-        <v>Melanie C</v>
+        <v>D.O.D</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L183" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>I'm Perfect</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:36</v>
+        <v>3:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L184" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>5:05</v>
+        <v>2:20</v>
       </c>
       <c r="H185" t="str">
-        <v>Anish Kumar</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L185" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Bitch You Weird</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G186" t="str">
-        <v>2:27</v>
+        <v>2:46</v>
       </c>
       <c r="H186" t="str">
-        <v>Real Boston Richey</v>
+        <v>Curren$y</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L186" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Blackbird Rising</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>24</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:24</v>
+        <v>3:25</v>
       </c>
       <c r="H187" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Chxrry</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L187" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>usher in the spirit</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H188" t="str">
-        <v>Aaron Cole</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L188" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Moonlight</v>
+        <v>So…</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Moonlight - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:23</v>
+        <v>3:16</v>
       </c>
       <c r="H189" t="str">
-        <v>Chelsea Plank</v>
+        <v>Ama</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L189" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:17</v>
+        <v>3:01</v>
       </c>
       <c r="H190" t="str">
-        <v>Becky Hill</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L190" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Closure</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Closure - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G191" t="str">
-        <v>2:27</v>
+        <v>4:13</v>
       </c>
       <c r="H191" t="str">
-        <v>D.O.D</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L191" t="str">
-        <v>Closure - D.O.D</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>HOTS 4 U</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:34</v>
+        <v>6:12</v>
       </c>
       <c r="H192" t="str">
-        <v>Chris Lorenzo</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L192" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>Puleza</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G193" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H193" t="str">
-        <v>ARIA VEGA</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L193" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>The Coin Toss</v>
+        <v>Bastards</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G194" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H194" t="str">
-        <v>Curren$y</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L194" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>Crutch</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:25</v>
+        <v>3:31</v>
       </c>
       <c r="H195" t="str">
-        <v>Chxrry</v>
+        <v>Love Spells</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L195" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Perfect For Me</v>
+        <v>Just A Man</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:02</v>
+        <v>2:38</v>
       </c>
       <c r="H196" t="str">
-        <v>Jamal Roberts</v>
+        <v>MOIO</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L196" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>So…</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>So… - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H197" t="str">
-        <v>Ama</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L197" t="str">
-        <v>So… - Ama</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>PASE Y PASE</v>
+        <v>Love You More</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:01</v>
+        <v>2:48</v>
       </c>
       <c r="H198" t="str">
-        <v>Tito Double P</v>
+        <v>Rudimental</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L198" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>Construct</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>ONE</v>
       </c>
       <c r="G199" t="str">
-        <v>4:13</v>
+        <v>3:57</v>
       </c>
       <c r="H199" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Sevendust</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L199" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Aljahalat</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Aljahalat - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G200" t="str">
-        <v>6:12</v>
+        <v>4:54</v>
       </c>
       <c r="H200" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Venom</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L200" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Puleza</v>
+        <v>Revenant</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>People of the Moon</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G201" t="str">
-        <v>3:47</v>
+        <v>3:31</v>
       </c>
       <c r="H201" t="str">
-        <v>Nu Genea</v>
+        <v>Loathe</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L201" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Bastards</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-01</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Bunny - EP</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:56</v>
+        <v>4:56</v>
       </c>
       <c r="H202" t="str">
-        <v>People I’ve Met</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L202" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Crutch</v>
+        <v>Power 4</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D203" t="str">
         <v>2026-05-01</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Crutch - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:31</v>
+        <v>1:40</v>
       </c>
       <c r="H203" t="str">
-        <v>Love Spells</v>
+        <v>slayr</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L203" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Just A Man</v>
+        <v>Too Easy</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D204" t="str">
         <v>2026-05-01</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Just A Man - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:38</v>
+        <v>4:14</v>
       </c>
       <c r="H204" t="str">
-        <v>MOIO</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L204" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Take Care Of You</v>
+        <v>If You Want It</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D205" t="str">
         <v>2026-05-01</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:51</v>
+        <v>3:56</v>
       </c>
       <c r="H205" t="str">
-        <v>Alina Baraz</v>
+        <v>ALAC</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L205" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Love You More</v>
+        <v>Shoplifting</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D206" t="str">
         <v>2026-05-01</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Love You More - Single</v>
+        <v>Theft World</v>
       </c>
       <c r="G206" t="str">
-        <v>2:48</v>
+        <v>3:02</v>
       </c>
       <c r="H206" t="str">
-        <v>Rudimental</v>
+        <v>Lip Critic</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
       </c>
       <c r="L206" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Shoplifting - Lip Critic</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Construct</v>
+        <v>Endlessly (feat. BEA1991)</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D207" t="str">
         <v>2026-05-01</v>
@@ -8241,334 +8241,30 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>ONE</v>
+        <v>Fold</v>
       </c>
       <c r="G207" t="str">
-        <v>3:57</v>
+        <v>5:57</v>
       </c>
       <c r="H207" t="str">
-        <v>Sevendust</v>
+        <v>Jump Source</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
       <c r="L207" t="str">
-        <v>Construct - Sevendust</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>As Above So Below</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Into Oblivion</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:54</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Venom</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
-      </c>
-      <c r="L208" t="str">
-        <v>As Above So Below - Venom</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Revenant</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>A Stranger To You</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:31</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Loathe</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Revenant - Loathe</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
-      </c>
-      <c r="G210" t="str">
-        <v>4:56</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Bear McCreary</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Power 4</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Power 4 - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>1:40</v>
-      </c>
-      <c r="H211" t="str">
-        <v>slayr</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Power 4 - slayr</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Too Easy</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Too Easy - Single</v>
-      </c>
-      <c r="G212" t="str">
-        <v>4:14</v>
-      </c>
-      <c r="H212" t="str">
-        <v>tig3r lewis</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
-      </c>
-      <c r="L212" t="str">
-        <v>Too Easy - tig3r lewis</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>If You Want It</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>If You Want It - Single</v>
-      </c>
-      <c r="G213" t="str">
-        <v>3:56</v>
-      </c>
-      <c r="H213" t="str">
-        <v>ALAC</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
-      </c>
-      <c r="L213" t="str">
-        <v>If You Want It - ALAC</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Shoplifting</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>Theft World</v>
-      </c>
-      <c r="G214" t="str">
-        <v>3:02</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Lip Critic</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
-      </c>
-      <c r="L214" t="str">
-        <v>Shoplifting - Lip Critic</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Endlessly (feat. BEA1991)</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Fold</v>
-      </c>
-      <c r="G215" t="str">
-        <v>5:57</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Jump Source</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
-      </c>
-      <c r="L215" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L215"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צוף מימון &amp; יקיר - שקוף</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410671&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Keith Urban</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צוף מימון &amp; יקיר - שקוף</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410670&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Danna</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אלשי שמואל - נכתב לנו מזמן</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410669&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Armik</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אלשי שמואל - נכתב לנו מזמן</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>איציק מארי - עוף מדבר</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-01</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410668&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Europe</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>איציק מארי - עוף מדבר</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>סקינרד You got this</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-01</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%a7%d7%99%d7%a0%d7%a8%d7%93-you-got-this/</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>הרכב הרגאיי-מטאל מניופורט, סקינרד Skindred, מוכרים כלהקה חיה סוחפת במיוחד, אבל האלבום “Smile” מ-2023 שינה את כללי המשחק. הוא הגיע למקום השני במצעדים בבריטניה, הוביל להופעת סולד אאוט באולם וומבלי ארנה, ולזכייה גאה בפרס להקת האלטרנטיב הטובה ביותר בטקס פרסי</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Foo Fighters</v>
       </c>
       <c r="I6" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>סקינרד You got this</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Keith Urban</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Danna</v>
+        <v>Muse</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Armik</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Europe</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Foo Fighters</v>
+        <v>Scorpions</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Muse</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-01</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Shaboozey</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-01</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Scorpions</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-01</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Meghan Trainor</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-01</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Lolo Zouaï</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-01</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Icona Pop</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Michael Jackson</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-01</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>The All-American Rejects</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-01</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Ringo Starr</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B25" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-01</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B26" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-01</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Demi Lovato</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-01</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Dean Lewis</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-01</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Matt Hansen</v>
+        <v>RUEL</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-01</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Ella Langley</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-01</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Meghan Trainor</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-01</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Lukas Graham</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-01</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Foo Fighters</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-01</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>RUEL</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-01</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Haiden Henderson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-01</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Conan Gray</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-01</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Foo Fighters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-01</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Ringo Starr</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Michael Bublé</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Malcolm Todd</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Sam Feldt</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Niall Horan</v>
+        <v>Danna</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Duran Duran</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Freya Skye</v>
+        <v>Cannons</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Beck</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Danna</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Cannons</v>
+        <v>Beck</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Beck</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Digster Pop Music</v>
+        <v>Madonna</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Beck</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>The All-American Rejects</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Armin van Buuren</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-01</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Demi Lovato</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Madonna</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Freya Ridings</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Celine Dion</v>
+        <v>ERNEST</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-01</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Peter Gabriel</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-01</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-01</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Jessie Ware</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-01</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-01</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>ERNEST</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-01</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-01</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Dean Lewis</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-01</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Bella White</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-01</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Kip Moore</v>
+        <v>Tyla</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-01</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-01</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Ben Gallaher</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-01</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Loreen</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-01</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Johnny Orlando</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-01</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tyla</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-01</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-01</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Lana Del Rey</v>
+        <v>Danna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-01</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Loreen</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-01</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Bonnie Tyler</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-01</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Tenille Townes</v>
+        <v>James Smith</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-01</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-01</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Danna</v>
+        <v>Ava Max</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-01</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>OneRepublic</v>
+        <v>John Summit</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-01</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>The Revivalists</v>
+        <v>Ava Max</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-01</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>James Smith</v>
+        <v>Danna</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-01</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Holly Humberstone</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-01</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Ava Max</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-01</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>John Summit</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-01</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Ava Max</v>
+        <v>bleachers</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-01</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Danna</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-01</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Conan Gray</v>
+        <v>LANY</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-01</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>TemplesOfficial</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-01</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Laufey</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-01</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>bleachers</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-01</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-01</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>LANY</v>
+        <v>florencemachine</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-01</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Scorpions</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-01</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-01</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>HAUSER</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-01</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-01</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>florencemachine</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-01</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Scorpions</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H102" t="str">
-        <v>Holly Humberstone</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L102" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>3:29</v>
       </c>
       <c r="H103" t="str">
-        <v>HAUSER</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L103" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>3:36</v>
       </c>
       <c r="H104" t="str">
-        <v>Holly Humberstone</v>
+        <v>Madonna</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L104" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B105" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>3 weeks ago</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>2:43</v>
       </c>
       <c r="H105" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L105" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Staying Still</v>
       </c>
       <c r="B106" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>3 weeks ago</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>4:28</v>
       </c>
       <c r="H106" t="str">
-        <v>Mae Muller</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L106" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:50</v>
+        <v>3:07</v>
       </c>
       <c r="H107" t="str">
-        <v>Zara Larsson</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L107" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Shape of a Woman</v>
+        <v>MUTT</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:29</v>
+        <v>1:59</v>
       </c>
       <c r="H108" t="str">
-        <v>Lady Gaga</v>
+        <v>NAV</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L108" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Bring Your Love</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CONFESSIONS II</v>
+        <v>Victory</v>
       </c>
       <c r="G109" t="str">
-        <v>3:36</v>
+        <v>3:27</v>
       </c>
       <c r="H109" t="str">
-        <v>Madonna</v>
+        <v>Madeon</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L109" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Horses and Divorces</v>
+        <v>Lioness</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Middle of Nowhere</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v>3:32</v>
       </c>
       <c r="H110" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L110" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Staying Still</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:28</v>
+        <v>2:19</v>
       </c>
       <c r="H111" t="str">
-        <v>Noah Kahan</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L111" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>Promise?</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:07</v>
+        <v>3:12</v>
       </c>
       <c r="H112" t="str">
-        <v>Alex Warren</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L112" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>MUTT</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>MUTT - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G113" t="str">
-        <v>1:59</v>
+        <v>2:32</v>
       </c>
       <c r="H113" t="str">
-        <v>NAV</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L113" t="str">
-        <v>MUTT - NAV</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>Material Lover</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Victory</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G114" t="str">
-        <v>3:27</v>
+        <v>2:58</v>
       </c>
       <c r="H114" t="str">
-        <v>Madeon</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L114" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Lioness</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>BROWN</v>
       </c>
       <c r="G115" t="str">
-        <v>3:32</v>
+        <v>4:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Maya Hawke</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L115" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>IT'S OK</v>
+        <v>Echo</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:19</v>
+        <v>2:15</v>
       </c>
       <c r="H116" t="str">
-        <v>Bryson Tiller</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L116" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Promise?</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Promise? - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G117" t="str">
-        <v>3:12</v>
+        <v>3:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Bella Kay</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L117" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cool Buzz</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Be Sweet To Me</v>
+        <v>CORSA</v>
       </c>
       <c r="G118" t="str">
-        <v>2:32</v>
+        <v>2:55</v>
       </c>
       <c r="H118" t="str">
-        <v>Violet Grohl</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L118" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Material Lover</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:58</v>
+        <v>5:35</v>
       </c>
       <c r="H119" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Maisak</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L119" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>BROWN</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:26</v>
+        <v>3:27</v>
       </c>
       <c r="H120" t="str">
-        <v>Chris Brown</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L120" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Echo</v>
+        <v>BITCH</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>BITCH</v>
       </c>
       <c r="G121" t="str">
-        <v>2:15</v>
+        <v>2:42</v>
       </c>
       <c r="H121" t="str">
-        <v>Daddy Yankee</v>
+        <v>Lizzo</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L121" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Cry Baby</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G122" t="str">
-        <v>3:52</v>
+        <v>2:27</v>
       </c>
       <c r="H122" t="str">
-        <v>Vince Staples</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L122" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Ricky Bobby</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>CORSA</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:55</v>
+        <v>3:09</v>
       </c>
       <c r="H123" t="str">
-        <v>Eladio Carrión</v>
+        <v>Halsey</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L123" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>5:35</v>
+        <v>2:44</v>
       </c>
       <c r="H124" t="str">
-        <v>Maisak</v>
+        <v>Labrinth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L124" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Don't Worry Baby</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G125" t="str">
-        <v>3:27</v>
+        <v>3:54</v>
       </c>
       <c r="H125" t="str">
-        <v>Dom Dolla</v>
+        <v>Bleachers</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L125" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>BITCH</v>
+        <v>Ruca</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>BITCH</v>
+        <v>MUDA</v>
       </c>
       <c r="G126" t="str">
-        <v>2:42</v>
+        <v>3:01</v>
       </c>
       <c r="H126" t="str">
-        <v>Lizzo</v>
+        <v>Carín León</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L126" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Just Wanna Cry</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:27</v>
+        <v>2:55</v>
       </c>
       <c r="H127" t="str">
-        <v>Meghan Trainor</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L127" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Carry the Weight</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>3:09</v>
+        <v>1:43</v>
       </c>
       <c r="H128" t="str">
-        <v>Halsey</v>
+        <v>North West</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L128" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>PROSTITUTE</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G129" t="str">
-        <v>2:44</v>
+        <v>3:09</v>
       </c>
       <c r="H129" t="str">
-        <v>Labrinth</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L129" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>i'm not joking</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>everyone for ten minutes</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:54</v>
+        <v>2:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Bleachers</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L130" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Ruca</v>
+        <v>Just A Man</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>MUDA</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:01</v>
+        <v>2:19</v>
       </c>
       <c r="H131" t="str">
-        <v>Carín León</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L131" t="str">
-        <v>Ruca - Carín León</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Make You Fight</v>
+        <v>The Observer</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Make You Fight - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G132" t="str">
-        <v>2:55</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Chris Lake</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L132" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>#N0rth4evr</v>
+        <v>Heroine</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>1:43</v>
+        <v>2:35</v>
       </c>
       <c r="H133" t="str">
-        <v>North West</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L133" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>BOY IN RED</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G134" t="str">
-        <v>3:09</v>
+        <v>4:10</v>
       </c>
       <c r="H134" t="str">
-        <v>Isaiah Rashad</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L134" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>EA EA EA</v>
+        <v>It's Me</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G135" t="str">
-        <v>2:42</v>
+        <v>2:18</v>
       </c>
       <c r="H135" t="str">
-        <v>Clave Especial</v>
+        <v>ILLIT</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L135" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Just A Man</v>
+        <v>the precipice</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Just A Man - Single</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>2:19</v>
+        <v>3:52</v>
       </c>
       <c r="H136" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L136" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>The Observer</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G137" t="str">
-        <v>2:50</v>
+        <v>2:58</v>
       </c>
       <c r="H137" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L137" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Heroine</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Heroine - Single</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:35</v>
+        <v>2:21</v>
       </c>
       <c r="H138" t="str">
-        <v>Maroon 5</v>
+        <v>BUNT.</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L138" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Do Me Right</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>FANTASYLAND</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:10</v>
+        <v>5:54</v>
       </c>
       <c r="H139" t="str">
-        <v>MR. FANTASY</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L139" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>It's Me</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:18</v>
+        <v>2:49</v>
       </c>
       <c r="H140" t="str">
-        <v>ILLIT</v>
+        <v>Robyn</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L140" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>the precipice</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:52</v>
+        <v>3:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Jessie Mazin</v>
+        <v>The-Dream</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L141" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Hello Lonesome</v>
+        <v>STAR</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>STAR</v>
       </c>
       <c r="G142" t="str">
-        <v>2:58</v>
+        <v>2:49</v>
       </c>
       <c r="H142" t="str">
-        <v>Cody Johnson</v>
+        <v>Tombochio</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L142" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G143" t="str">
-        <v>2:21</v>
+        <v>3:37</v>
       </c>
       <c r="H143" t="str">
-        <v>BUNT.</v>
+        <v>ERNEST</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L143" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>Evergreen</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G144" t="str">
-        <v>5:54</v>
+        <v>3:41</v>
       </c>
       <c r="H144" t="str">
-        <v>Ludwig Göransson</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L144" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G145" t="str">
-        <v>2:49</v>
+        <v>3:43</v>
       </c>
       <c r="H145" t="str">
-        <v>Robyn</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L145" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bring That Body</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Bring That Body - Single</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G146" t="str">
-        <v>3:34</v>
+        <v>3:11</v>
       </c>
       <c r="H146" t="str">
-        <v>The-Dream</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L146" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>STAR</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>STAR</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G147" t="str">
-        <v>2:49</v>
+        <v>3:16</v>
       </c>
       <c r="H147" t="str">
-        <v>Tombochio</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L147" t="str">
-        <v>STAR - Tombochio</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>What’s A Little Rain</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Deep Blue</v>
+        <v>flow state</v>
       </c>
       <c r="G148" t="str">
-        <v>3:37</v>
+        <v>4:00</v>
       </c>
       <c r="H148" t="str">
-        <v>ERNEST</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L148" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Evergreen</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Victory Garden</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G149" t="str">
-        <v>3:41</v>
+        <v>4:27</v>
       </c>
       <c r="H149" t="str">
-        <v>Young the Giant</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L149" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>She Does It Right</v>
+        <v>My Life</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Peaches!</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G150" t="str">
-        <v>3:43</v>
+        <v>3:31</v>
       </c>
       <c r="H150" t="str">
-        <v>The Black Keys</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L150" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Punching the Flowers</v>
+        <v>Ribcage</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>I Built You A Tower</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H151" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L151" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>How Did You Know</v>
+        <v>i loved you then</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G152" t="str">
-        <v>3:16</v>
+        <v>3:42</v>
       </c>
       <c r="H152" t="str">
-        <v>Jon Pardi</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L152" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Summer Breeze</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>flow state</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G153" t="str">
-        <v>4:00</v>
+        <v>3:54</v>
       </c>
       <c r="H153" t="str">
-        <v>Keith Urban</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L153" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Sound of a Woman</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Sound of a Woman</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G154" t="str">
-        <v>4:27</v>
+        <v>2:53</v>
       </c>
       <c r="H154" t="str">
-        <v>Rita Wilson</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L154" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>My Life</v>
+        <v>The Author</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>BERNARR.</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:31</v>
+        <v>4:36</v>
       </c>
       <c r="H155" t="str">
-        <v>Durand Bernarr</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L155" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Ribcage</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Ribcage - Single</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:00</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Bella Poarch</v>
+        <v>Trousdale</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L156" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>i loved you then</v>
+        <v>RUIN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G157" t="str">
-        <v>3:42</v>
+        <v>3:23</v>
       </c>
       <c r="H157" t="str">
-        <v>Alana Springsteen</v>
+        <v>HEALTH</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L157" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>I'll Let You Finish</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Fire From The Hip</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:54</v>
+        <v>2:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Finn Wolfhard</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L158" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>It Gets Me Through</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:53</v>
+        <v>2:50</v>
       </c>
       <c r="H159" t="str">
-        <v>Laura Marano</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L159" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>The Author</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>The Author - Single</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:36</v>
+        <v>3:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Brandon Lake</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L160" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G161" t="str">
-        <v>3:44</v>
+        <v>2:33</v>
       </c>
       <c r="H161" t="str">
-        <v>Trousdale</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L161" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>RUIN</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>ADDENDUM</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H162" t="str">
-        <v>HEALTH</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L162" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I Know I Know</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>I Know I Know - Single</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:39</v>
+        <v>3:02</v>
       </c>
       <c r="H163" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L163" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drive All Night</v>
+        <v>Hallucination</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Drive All Night - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>2:50</v>
+        <v>3:22</v>
       </c>
       <c r="H164" t="str">
-        <v>Wyatt Flores</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L164" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:41</v>
+        <v>2:44</v>
       </c>
       <c r="H165" t="str">
-        <v>Jessie Reyez</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L165" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Boys In Blue</v>
+        <v>Fall Short</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Emotional Junglist</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:33</v>
+        <v>2:44</v>
       </c>
       <c r="H166" t="str">
-        <v>Nia Archives</v>
+        <v>nyan</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L166" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Salma Hayek</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G167" t="str">
-        <v>3:43</v>
+        <v>3:34</v>
       </c>
       <c r="H167" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Kneecap</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L167" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Stubborn Mouth</v>
+        <v>1989</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>3:05</v>
       </c>
       <c r="H168" t="str">
-        <v>Girl Tones</v>
+        <v>Nightly</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L168" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Hallucination</v>
+        <v>no more regrets</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>2:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Isabel LaRosa</v>
+        <v>almost monday</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L169" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>In Da Jungle</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G170" t="str">
-        <v>2:44</v>
+        <v>3:16</v>
       </c>
       <c r="H170" t="str">
-        <v>BLOND:ISH</v>
+        <v>Melanie C</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L170" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Fall Short</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Fall Short - Single</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:44</v>
+        <v>2:36</v>
       </c>
       <c r="H171" t="str">
-        <v>nyan</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L171" t="str">
-        <v>Fall Short - nyan</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>FENIAN</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>3:34</v>
+        <v>5:05</v>
       </c>
       <c r="H172" t="str">
-        <v>Kneecap</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L172" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>1989</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>1989 - Single</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:05</v>
+        <v>2:27</v>
       </c>
       <c r="H173" t="str">
-        <v>Nightly</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L173" t="str">
-        <v>1989 - Nightly</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>no more regrets</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>no more regrets - Single</v>
+        <v>24</v>
       </c>
       <c r="G174" t="str">
-        <v>2:58</v>
+        <v>2:24</v>
       </c>
       <c r="H174" t="str">
-        <v>almost monday</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L174" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Drum Machine</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Sweat</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:16</v>
+        <v>3:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Melanie C</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L175" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>I'm Perfect</v>
+        <v>Moonlight</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:36</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L176" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>5:05</v>
+        <v>2:17</v>
       </c>
       <c r="H177" t="str">
-        <v>Anish Kumar</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L177" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Bitch You Weird</v>
+        <v>Closure</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G178" t="str">
         <v>2:27</v>
       </c>
       <c r="H178" t="str">
-        <v>Real Boston Richey</v>
+        <v>D.O.D</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L178" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Blackbird Rising</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>24</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:24</v>
+        <v>3:34</v>
       </c>
       <c r="H179" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L179" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>usher in the spirit</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:00</v>
+        <v>2:20</v>
       </c>
       <c r="H180" t="str">
-        <v>Aaron Cole</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L180" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Moonlight</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Moonlight - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Chelsea Plank</v>
+        <v>Curren$y</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L181" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:17</v>
+        <v>3:25</v>
       </c>
       <c r="H182" t="str">
-        <v>Becky Hill</v>
+        <v>Chxrry</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L182" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Closure</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Closure - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:27</v>
+        <v>3:02</v>
       </c>
       <c r="H183" t="str">
-        <v>D.O.D</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L183" t="str">
-        <v>Closure - D.O.D</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>HOTS 4 U</v>
+        <v>So…</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:34</v>
+        <v>3:16</v>
       </c>
       <c r="H184" t="str">
-        <v>Chris Lorenzo</v>
+        <v>Ama</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L184" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:20</v>
+        <v>3:01</v>
       </c>
       <c r="H185" t="str">
-        <v>ARIA VEGA</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L185" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The Coin Toss</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G186" t="str">
-        <v>2:46</v>
+        <v>4:13</v>
       </c>
       <c r="H186" t="str">
-        <v>Curren$y</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L186" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:25</v>
+        <v>6:12</v>
       </c>
       <c r="H187" t="str">
-        <v>Chxrry</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L187" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Perfect For Me</v>
+        <v>Puleza</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G188" t="str">
-        <v>3:02</v>
+        <v>3:47</v>
       </c>
       <c r="H188" t="str">
-        <v>Jamal Roberts</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L188" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>So…</v>
+        <v>Bastards</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>So… - Single</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>3:16</v>
+        <v>2:56</v>
       </c>
       <c r="H189" t="str">
-        <v>Ama</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L189" t="str">
-        <v>So… - Ama</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>PASE Y PASE</v>
+        <v>Crutch</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H190" t="str">
-        <v>Tito Double P</v>
+        <v>Love Spells</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L190" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>Just A Man</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:13</v>
+        <v>2:38</v>
       </c>
       <c r="H191" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>MOIO</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L191" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Aljahalat</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Aljahalat - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>6:12</v>
+        <v>3:51</v>
       </c>
       <c r="H192" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L192" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Puleza</v>
+        <v>Love You More</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>People of the Moon</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:47</v>
+        <v>2:48</v>
       </c>
       <c r="H193" t="str">
-        <v>Nu Genea</v>
+        <v>Rudimental</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L193" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Bastards</v>
+        <v>Construct</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Bunny - EP</v>
+        <v>ONE</v>
       </c>
       <c r="G194" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H194" t="str">
-        <v>People I’ve Met</v>
+        <v>Sevendust</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L194" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Crutch</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Crutch - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G195" t="str">
-        <v>3:31</v>
+        <v>4:54</v>
       </c>
       <c r="H195" t="str">
-        <v>Love Spells</v>
+        <v>Venom</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L195" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Just A Man</v>
+        <v>Revenant</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Just A Man - Single</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G196" t="str">
-        <v>2:38</v>
+        <v>3:31</v>
       </c>
       <c r="H196" t="str">
-        <v>MOIO</v>
+        <v>Loathe</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L196" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Take Care Of You</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:51</v>
+        <v>4:56</v>
       </c>
       <c r="H197" t="str">
-        <v>Alina Baraz</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L197" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Love You More</v>
+        <v>Power 4</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Love You More - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:48</v>
+        <v>1:40</v>
       </c>
       <c r="H198" t="str">
-        <v>Rudimental</v>
+        <v>slayr</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L198" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Construct</v>
+        <v>Too Easy</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>ONE</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:57</v>
+        <v>4:14</v>
       </c>
       <c r="H199" t="str">
-        <v>Sevendust</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L199" t="str">
-        <v>Construct - Sevendust</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>As Above So Below</v>
+        <v>If You Want It</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Into Oblivion</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:54</v>
+        <v>3:56</v>
       </c>
       <c r="H200" t="str">
-        <v>Venom</v>
+        <v>ALAC</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L200" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Revenant</v>
+        <v>Shoplifting</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>A Stranger To You</v>
+        <v>Theft World</v>
       </c>
       <c r="G201" t="str">
-        <v>3:31</v>
+        <v>3:02</v>
       </c>
       <c r="H201" t="str">
-        <v>Loathe</v>
+        <v>Lip Critic</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
       </c>
       <c r="L201" t="str">
-        <v>Revenant - Loathe</v>
+        <v>Shoplifting - Lip Critic</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Endlessly (feat. BEA1991)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-01</v>
@@ -8051,220 +8051,30 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>Fold</v>
       </c>
       <c r="G202" t="str">
-        <v>4:56</v>
+        <v>5:57</v>
       </c>
       <c r="H202" t="str">
-        <v>Bear McCreary</v>
+        <v>Jump Source</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
       <c r="L202" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Power 4</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Power 4 - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>1:40</v>
-      </c>
-      <c r="H203" t="str">
-        <v>slayr</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Power 4 - slayr</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Too Easy</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Too Easy - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>4:14</v>
-      </c>
-      <c r="H204" t="str">
-        <v>tig3r lewis</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Too Easy - tig3r lewis</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>If You Want It</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>If You Want It - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:56</v>
-      </c>
-      <c r="H205" t="str">
-        <v>ALAC</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
-      </c>
-      <c r="L205" t="str">
-        <v>If You Want It - ALAC</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Shoplifting</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Theft World</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:02</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Lip Critic</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Shoplifting - Lip Critic</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Endlessly (feat. BEA1991)</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Fold</v>
-      </c>
-      <c r="G207" t="str">
-        <v>5:57</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Jump Source</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
-      </c>
-      <c r="L207" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>

--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>מיקה קרני ואודי תורג'מן - ברית</v>
       </c>
       <c r="B2" t="str">
-        <v>2d ago</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24466&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2d ago</v>
+        <v>19:31</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Keith Urban</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>מיקה קרני ואודי תורג'מן - ברית</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Danna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Armik</v>
+        <v>Danna</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Europe</v>
+        <v>Armik</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-01</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Foo Fighters</v>
+        <v>Europe</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Muse</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B9" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Muse</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>6d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Shaboozey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Scorpions</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Meghan Trainor</v>
+        <v>Scorpions</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Icona Pop</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Michael Jackson</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>The All-American Rejects</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Ringo Starr</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-01</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-01</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Ella Langley</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-01</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-01</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lukas Graham</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-01</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Foo Fighters</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-01</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>RUEL</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-01</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Haiden Henderson</v>
+        <v>RUEL</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Conan Gray</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Foo Fighters</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-01</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bublé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Malcolm Todd</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Sam Feldt</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Niall Horan</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B37" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-01</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B38" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Duran Duran</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Freya Skye</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B40" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B41" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Danna</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Danna</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Beck</v>
+        <v>Cannons</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Beck</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B48" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Digster Pop Music</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B49" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Beck</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The All-American Rejects</v>
+        <v>Beck</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Armin van Buuren</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Madonna</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Freya Ridings</v>
+        <v>Madonna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Celine Dion</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Peter Gabriel</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-01</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>ERNEST</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-01</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>ERNEST</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dean Lewis</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-01</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kip Moore</v>
+        <v>Bella White</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-01</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-01</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Ben Gallaher</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-01</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Johnny Orlando</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-01</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Tyla</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Tyla</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lana Del Rey</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Loreen</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Loreen</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tenille Townes</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Danna</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>OneRepublic</v>
+        <v>Danna</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Revivalists</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>James Smith</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Holly Humberstone</v>
+        <v>James Smith</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-01</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ava Max</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-01</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>John Summit</v>
+        <v>Ava Max</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-01</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Ava Max</v>
+        <v>John Summit</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-01</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Danna</v>
+        <v>Ava Max</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-01</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Conan Gray</v>
+        <v>Danna</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-01</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>TemplesOfficial</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-01</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-01</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>bleachers</v>
+        <v>Laufey</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-01</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Nothing But Thieves</v>
+        <v>bleachers</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-01</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>LANY</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-01</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>LANY</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-01</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-01</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-01</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Kygo and carter faith</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-01</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>florencemachine</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-01</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Scorpions</v>
+        <v>florencemachine</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-01</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-01</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-01</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-01</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Mae Muller</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Zara Larsson</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shape of a Woman</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G103" t="str">
-        <v>3:29</v>
+        <v>2:50</v>
       </c>
       <c r="H103" t="str">
-        <v>Lady Gaga</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L103" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Bring Your Love</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>CONFESSIONS II</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G104" t="str">
-        <v>3:36</v>
+        <v>3:29</v>
       </c>
       <c r="H104" t="str">
-        <v>Madonna</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L104" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Horses and Divorces</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Middle of Nowhere</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G105" t="str">
-        <v>2:43</v>
+        <v>3:36</v>
       </c>
       <c r="H105" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Madonna</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L105" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Staying Still</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G106" t="str">
-        <v>4:28</v>
+        <v>2:43</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L106" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>Staying Still</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G107" t="str">
-        <v>3:07</v>
+        <v>4:28</v>
       </c>
       <c r="H107" t="str">
-        <v>Alex Warren</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L107" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>MUTT</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>MUTT - Single</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>1:59</v>
+        <v>3:07</v>
       </c>
       <c r="H108" t="str">
-        <v>NAV</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L108" t="str">
-        <v>MUTT - NAV</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>MUTT</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Victory</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:27</v>
+        <v>1:59</v>
       </c>
       <c r="H109" t="str">
-        <v>Madeon</v>
+        <v>NAV</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L109" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Lioness</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Victory</v>
       </c>
       <c r="G110" t="str">
-        <v>3:32</v>
+        <v>3:27</v>
       </c>
       <c r="H110" t="str">
-        <v>Maya Hawke</v>
+        <v>Madeon</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L110" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>IT'S OK</v>
+        <v>Lioness</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>IT'S OK - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G111" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H111" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L111" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Promise?</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Promise? - Single</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:12</v>
+        <v>2:19</v>
       </c>
       <c r="H112" t="str">
-        <v>Bella Kay</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L112" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Cool Buzz</v>
+        <v>Promise?</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:32</v>
+        <v>3:12</v>
       </c>
       <c r="H113" t="str">
-        <v>Violet Grohl</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L113" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Material Lover</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G114" t="str">
-        <v>2:58</v>
+        <v>2:32</v>
       </c>
       <c r="H114" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L114" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Material Lover</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>BROWN</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G115" t="str">
-        <v>4:26</v>
+        <v>2:58</v>
       </c>
       <c r="H115" t="str">
-        <v>Chris Brown</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L115" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Echo</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>BROWN</v>
       </c>
       <c r="G116" t="str">
-        <v>2:15</v>
+        <v>4:26</v>
       </c>
       <c r="H116" t="str">
-        <v>Daddy Yankee</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L116" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Echo</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Cry Baby</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:52</v>
+        <v>2:15</v>
       </c>
       <c r="H117" t="str">
-        <v>Vince Staples</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L117" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Ricky Bobby</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>CORSA</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G118" t="str">
-        <v>2:55</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Eladio Carrión</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L118" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>CORSA</v>
       </c>
       <c r="G119" t="str">
-        <v>5:35</v>
+        <v>2:55</v>
       </c>
       <c r="H119" t="str">
-        <v>Maisak</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L119" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Don't Worry Baby</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:27</v>
+        <v>5:35</v>
       </c>
       <c r="H120" t="str">
-        <v>Dom Dolla</v>
+        <v>Maisak</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L120" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:42</v>
+        <v>3:27</v>
       </c>
       <c r="H121" t="str">
-        <v>Lizzo</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L121" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Just Wanna Cry</v>
+        <v>BITCH</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>BITCH</v>
       </c>
       <c r="G122" t="str">
-        <v>2:27</v>
+        <v>2:42</v>
       </c>
       <c r="H122" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lizzo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L122" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Carry the Weight</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H123" t="str">
-        <v>Halsey</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L123" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PROSTITUTE</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:44</v>
+        <v>3:09</v>
       </c>
       <c r="H124" t="str">
-        <v>Labrinth</v>
+        <v>Halsey</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L124" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>i'm not joking</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>everyone for ten minutes</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G125" t="str">
-        <v>3:54</v>
+        <v>2:44</v>
       </c>
       <c r="H125" t="str">
-        <v>Bleachers</v>
+        <v>Labrinth</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L125" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Ruca</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>MUDA</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G126" t="str">
-        <v>3:01</v>
+        <v>3:54</v>
       </c>
       <c r="H126" t="str">
-        <v>Carín León</v>
+        <v>Bleachers</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L126" t="str">
-        <v>Ruca - Carín León</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Make You Fight</v>
+        <v>Ruca</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Make You Fight - Single</v>
+        <v>MUDA</v>
       </c>
       <c r="G127" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H127" t="str">
-        <v>Chris Lake</v>
+        <v>Carín León</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L127" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>#N0rth4evr</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>1:43</v>
+        <v>2:55</v>
       </c>
       <c r="H128" t="str">
-        <v>North West</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L128" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOY IN RED</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G129" t="str">
-        <v>3:09</v>
+        <v>1:43</v>
       </c>
       <c r="H129" t="str">
-        <v>Isaiah Rashad</v>
+        <v>North West</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L129" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>EA EA EA</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G130" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H130" t="str">
-        <v>Clave Especial</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L130" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Just A Man</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Just A Man - Single</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>2:19</v>
+        <v>2:42</v>
       </c>
       <c r="H131" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L131" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>The Observer</v>
+        <v>Just A Man</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>2:19</v>
       </c>
       <c r="H132" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L132" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Heroine</v>
+        <v>The Observer</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heroine - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G133" t="str">
-        <v>2:35</v>
+        <v>2:50</v>
       </c>
       <c r="H133" t="str">
-        <v>Maroon 5</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L133" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Do Me Right</v>
+        <v>Heroine</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FANTASYLAND</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:10</v>
+        <v>2:35</v>
       </c>
       <c r="H134" t="str">
-        <v>MR. FANTASY</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L134" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>It's Me</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G135" t="str">
-        <v>2:18</v>
+        <v>4:10</v>
       </c>
       <c r="H135" t="str">
-        <v>ILLIT</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L135" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>the precipice</v>
+        <v>It's Me</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H136" t="str">
-        <v>Jessie Mazin</v>
+        <v>ILLIT</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L136" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Hello Lonesome</v>
+        <v>the precipice</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G137" t="str">
-        <v>2:58</v>
+        <v>3:52</v>
       </c>
       <c r="H137" t="str">
-        <v>Cody Johnson</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L137" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G138" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H138" t="str">
-        <v>BUNT.</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L138" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>5:54</v>
+        <v>2:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Ludwig Göransson</v>
+        <v>BUNT.</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:49</v>
+        <v>5:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Robyn</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Bring That Body</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bring That Body - Single</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H141" t="str">
-        <v>The-Dream</v>
+        <v>Robyn</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L141" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>STAR</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>STAR</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Tombochio</v>
+        <v>The-Dream</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L142" t="str">
-        <v>STAR - Tombochio</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>What’s A Little Rain</v>
+        <v>STAR</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Deep Blue</v>
+        <v>STAR</v>
       </c>
       <c r="G143" t="str">
-        <v>3:37</v>
+        <v>2:49</v>
       </c>
       <c r="H143" t="str">
-        <v>ERNEST</v>
+        <v>Tombochio</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L143" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Evergreen</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Victory Garden</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G144" t="str">
-        <v>3:41</v>
+        <v>3:37</v>
       </c>
       <c r="H144" t="str">
-        <v>Young the Giant</v>
+        <v>ERNEST</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L144" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>She Does It Right</v>
+        <v>Evergreen</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Peaches!</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G145" t="str">
-        <v>3:43</v>
+        <v>3:41</v>
       </c>
       <c r="H145" t="str">
-        <v>The Black Keys</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L145" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Punching the Flowers</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>I Built You A Tower</v>
+        <v>Peaches!</v>
       </c>
       <c r="G146" t="str">
-        <v>3:11</v>
+        <v>3:43</v>
       </c>
       <c r="H146" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L146" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>How Did You Know</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G147" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H147" t="str">
-        <v>Jon Pardi</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L147" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Summer Breeze</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>flow state</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G148" t="str">
-        <v>4:00</v>
+        <v>3:16</v>
       </c>
       <c r="H148" t="str">
-        <v>Keith Urban</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L148" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Sound of a Woman</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Sound of a Woman</v>
+        <v>flow state</v>
       </c>
       <c r="G149" t="str">
-        <v>4:27</v>
+        <v>4:00</v>
       </c>
       <c r="H149" t="str">
-        <v>Rita Wilson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L149" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>My Life</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>BERNARR.</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G150" t="str">
-        <v>3:31</v>
+        <v>4:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Durand Bernarr</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L150" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ribcage</v>
+        <v>My Life</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ribcage - Single</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G151" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H151" t="str">
-        <v>Bella Poarch</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L151" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>i loved you then</v>
+        <v>Ribcage</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:42</v>
+        <v>3:00</v>
       </c>
       <c r="H152" t="str">
-        <v>Alana Springsteen</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L152" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>I'll Let You Finish</v>
+        <v>i loved you then</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Fire From The Hip</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G153" t="str">
-        <v>3:54</v>
+        <v>3:42</v>
       </c>
       <c r="H153" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L153" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>It Gets Me Through</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G154" t="str">
-        <v>2:53</v>
+        <v>3:54</v>
       </c>
       <c r="H154" t="str">
-        <v>Laura Marano</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L154" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>The Author</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Author - Single</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G155" t="str">
-        <v>4:36</v>
+        <v>2:53</v>
       </c>
       <c r="H155" t="str">
-        <v>Brandon Lake</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L155" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>The Author</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>4:36</v>
       </c>
       <c r="H156" t="str">
-        <v>Trousdale</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L156" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>RUIN</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>ADDENDUM</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>HEALTH</v>
+        <v>Trousdale</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L157" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>I Know I Know</v>
+        <v>RUIN</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>I Know I Know - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G158" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H158" t="str">
-        <v>STELLA LEFTY</v>
+        <v>HEALTH</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L158" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Drive All Night</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Drive All Night - Single</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Wyatt Flores</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L159" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H160" t="str">
-        <v>Jessie Reyez</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L160" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Boys In Blue</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Emotional Junglist</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:33</v>
+        <v>3:41</v>
       </c>
       <c r="H161" t="str">
-        <v>Nia Archives</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L161" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Salma Hayek</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G162" t="str">
-        <v>3:43</v>
+        <v>2:33</v>
       </c>
       <c r="H162" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L162" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Stubborn Mouth</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:02</v>
+        <v>3:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Girl Tones</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L163" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Hallucination</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:22</v>
+        <v>3:02</v>
       </c>
       <c r="H164" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L164" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>In Da Jungle</v>
+        <v>Hallucination</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>2:44</v>
+        <v>3:22</v>
       </c>
       <c r="H165" t="str">
-        <v>BLOND:ISH</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L165" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Fall Short</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Fall Short - Single</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G166" t="str">
         <v>2:44</v>
       </c>
       <c r="H166" t="str">
-        <v>nyan</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L166" t="str">
-        <v>Fall Short - nyan</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>Fall Short</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>FENIAN</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H167" t="str">
-        <v>Kneecap</v>
+        <v>nyan</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L167" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>1989</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>1989 - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G168" t="str">
-        <v>3:05</v>
+        <v>3:34</v>
       </c>
       <c r="H168" t="str">
-        <v>Nightly</v>
+        <v>Kneecap</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L168" t="str">
-        <v>1989 - Nightly</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>no more regrets</v>
+        <v>1989</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>no more regrets - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H169" t="str">
-        <v>almost monday</v>
+        <v>Nightly</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L169" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drum Machine</v>
+        <v>no more regrets</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Sweat</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:16</v>
+        <v>2:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Melanie C</v>
+        <v>almost monday</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L170" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>I'm Perfect</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G171" t="str">
-        <v>2:36</v>
+        <v>3:16</v>
       </c>
       <c r="H171" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Melanie C</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L171" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>5:05</v>
+        <v>2:36</v>
       </c>
       <c r="H172" t="str">
-        <v>Anish Kumar</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L172" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Bitch You Weird</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>2:27</v>
+        <v>5:05</v>
       </c>
       <c r="H173" t="str">
-        <v>Real Boston Richey</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L173" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Blackbird Rising</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>24</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:24</v>
+        <v>2:27</v>
       </c>
       <c r="H174" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L174" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>usher in the spirit</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>24</v>
       </c>
       <c r="G175" t="str">
-        <v>3:00</v>
+        <v>2:24</v>
       </c>
       <c r="H175" t="str">
-        <v>Aaron Cole</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L175" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Moonlight</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Moonlight - Single</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>3:00</v>
       </c>
       <c r="H176" t="str">
-        <v>Chelsea Plank</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L176" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Moonlight</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:17</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>Becky Hill</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Closure</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Closure - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:27</v>
+        <v>2:17</v>
       </c>
       <c r="H178" t="str">
-        <v>D.O.D</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L178" t="str">
-        <v>Closure - D.O.D</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>HOTS 4 U</v>
+        <v>Closure</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H179" t="str">
-        <v>Chris Lorenzo</v>
+        <v>D.O.D</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L179" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:20</v>
+        <v>3:34</v>
       </c>
       <c r="H180" t="str">
-        <v>ARIA VEGA</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The Coin Toss</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>2:20</v>
       </c>
       <c r="H181" t="str">
-        <v>Curren$y</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L181" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G182" t="str">
-        <v>3:25</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Chxrry</v>
+        <v>Curren$y</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L182" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Perfect For Me</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:02</v>
+        <v>3:25</v>
       </c>
       <c r="H183" t="str">
-        <v>Jamal Roberts</v>
+        <v>Chxrry</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L183" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>So…</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>So… - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:16</v>
+        <v>3:02</v>
       </c>
       <c r="H184" t="str">
-        <v>Ama</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L184" t="str">
-        <v>So… - Ama</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>PASE Y PASE</v>
+        <v>So…</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:01</v>
+        <v>3:16</v>
       </c>
       <c r="H185" t="str">
-        <v>Tito Double P</v>
+        <v>Ama</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L185" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:13</v>
+        <v>3:01</v>
       </c>
       <c r="H186" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L186" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Aljahalat</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Aljahalat - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G187" t="str">
-        <v>6:12</v>
+        <v>4:13</v>
       </c>
       <c r="H187" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L187" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Puleza</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>People of the Moon</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:47</v>
+        <v>6:12</v>
       </c>
       <c r="H188" t="str">
-        <v>Nu Genea</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L188" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Bastards</v>
+        <v>Puleza</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Bunny - EP</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G189" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H189" t="str">
-        <v>People I’ve Met</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L189" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Crutch</v>
+        <v>Bastards</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Crutch - Single</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>3:31</v>
+        <v>2:56</v>
       </c>
       <c r="H190" t="str">
-        <v>Love Spells</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L190" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Just A Man</v>
+        <v>Crutch</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Just A Man - Single</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:38</v>
+        <v>3:31</v>
       </c>
       <c r="H191" t="str">
-        <v>MOIO</v>
+        <v>Love Spells</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L191" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Take Care Of You</v>
+        <v>Just A Man</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:51</v>
+        <v>2:38</v>
       </c>
       <c r="H192" t="str">
-        <v>Alina Baraz</v>
+        <v>MOIO</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L192" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Love You More</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Love You More - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:48</v>
+        <v>3:51</v>
       </c>
       <c r="H193" t="str">
-        <v>Rudimental</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L193" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Construct</v>
+        <v>Love You More</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>ONE</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:57</v>
+        <v>2:48</v>
       </c>
       <c r="H194" t="str">
-        <v>Sevendust</v>
+        <v>Rudimental</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L194" t="str">
-        <v>Construct - Sevendust</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>As Above So Below</v>
+        <v>Construct</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Into Oblivion</v>
+        <v>ONE</v>
       </c>
       <c r="G195" t="str">
-        <v>4:54</v>
+        <v>3:57</v>
       </c>
       <c r="H195" t="str">
-        <v>Venom</v>
+        <v>Sevendust</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L195" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Revenant</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>A Stranger To You</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G196" t="str">
-        <v>3:31</v>
+        <v>4:54</v>
       </c>
       <c r="H196" t="str">
-        <v>Loathe</v>
+        <v>Venom</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L196" t="str">
-        <v>Revenant - Loathe</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Revenant</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G197" t="str">
-        <v>4:56</v>
+        <v>3:31</v>
       </c>
       <c r="H197" t="str">
-        <v>Bear McCreary</v>
+        <v>Loathe</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Power 4</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Power 4 - Single</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>1:40</v>
+        <v>4:56</v>
       </c>
       <c r="H198" t="str">
-        <v>slayr</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L198" t="str">
-        <v>Power 4 - slayr</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Too Easy</v>
+        <v>Power 4</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Too Easy - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:14</v>
+        <v>1:40</v>
       </c>
       <c r="H199" t="str">
-        <v>tig3r lewis</v>
+        <v>slayr</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L199" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>If You Want It</v>
+        <v>Too Easy</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>If You Want It - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:56</v>
+        <v>4:14</v>
       </c>
       <c r="H200" t="str">
-        <v>ALAC</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L200" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Shoplifting</v>
+        <v>If You Want It</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-01</v>
@@ -8013,68 +8013,106 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Theft World</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:02</v>
+        <v>3:56</v>
       </c>
       <c r="H201" t="str">
-        <v>Lip Critic</v>
+        <v>ALAC</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L201" t="str">
-        <v>Shoplifting - Lip Critic</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Shoplifting</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Theft World</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Lip Critic</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Shoplifting - Lip Critic</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
         <v>Endlessly (feat. BEA1991)</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D203" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
         <v>Fold</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G203" t="str">
         <v>5:57</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H203" t="str">
         <v>Jump Source</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
         <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K203" t="str">
         <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L203" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה קרני ואודי תורג'מן - ברית</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24466&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:31</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Keith Urban</v>
       </c>
       <c r="I2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה קרני ואודי תורג'מן - ברית</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-01</v>
@@ -495,7 +495,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Keith Urban</v>
+        <v>Danna</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Danna</v>
+        <v>Armik</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B5" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-01</v>
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Armik</v>
+        <v>Europe</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B6" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-01</v>
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Europe</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Lady Gaga, Doechii - RUNWAY</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Foo Fighters</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Muse</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Muse</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Shaboozey</v>
+        <v>Scorpions</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-01</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Scorpions</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-01</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B14" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-01</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B15" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-01</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-01</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-01</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Icona Pop</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B18" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-01</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Michael Jackson</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-01</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>The All-American Rejects</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B20" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-01</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Ringo Starr</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-01</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-01</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Demi Lovato</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-01</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dean Lewis</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-01</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Matt Hansen</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B25" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-01</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Ella Langley</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B26" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-01</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-01</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Lukas Graham</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-01</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Foo Fighters</v>
+        <v>RUEL</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-01</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>RUEL</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-01</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Haiden Henderson</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-01</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Conan Gray</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-01</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Foo Fighters</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-01</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ringo Starr</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-01</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Michael Bublé</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-01</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Malcolm Todd</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Sam Feldt</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B37" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-01</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Niall Horan</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-01</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Duran Duran</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Freya Skye</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Danna</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Danna</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B44" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-01</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cannons</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Cannons</v>
+        <v>Beck</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Beck</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B48" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-01</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B49" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-01</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Digster Pop Music</v>
+        <v>Beck</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-01</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Beck</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The All-American Rejects</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-01</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-01</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Demi Lovato</v>
+        <v>Madonna</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Madonna</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-01</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Freya Ridings</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-01</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Celine Dion</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-01</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Peter Gabriel</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-01</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-01</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Jessie Ware</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-01</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>The Kid LAROI.</v>
+        <v>ERNEST</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-01</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>ERNEST</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-01</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-01</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Dean Lewis</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-01</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Bella White</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-01</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Kip Moore</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-01</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-01</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Ben Gallaher</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-01</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-01</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Johnny Orlando</v>
+        <v>Tyla</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-01</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Tyla</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-01</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-01</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Lana Del Rey</v>
+        <v>Loreen</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-01</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Loreen</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-01</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-01</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Tenille Townes</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-01</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Danna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-01</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Danna</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-01</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>OneRepublic</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-01</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>The Revivalists</v>
+        <v>James Smith</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-01</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>James Smith</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-01</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Holly Humberstone</v>
+        <v>Ava Max</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-01</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Ava Max</v>
+        <v>John Summit</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-01</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>John Summit</v>
+        <v>Ava Max</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-01</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Ava Max</v>
+        <v>Danna</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-01</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Danna</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-01</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Conan Gray</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-01</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>TemplesOfficial</v>
+        <v>Laufey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-01</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Laufey</v>
+        <v>bleachers</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-01</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>bleachers</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-01</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Nothing But Thieves</v>
+        <v>LANY</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-01</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>LANY</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-01</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-01</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-01</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-01</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Kygo and carter faith</v>
+        <v>florencemachine</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-01</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>florencemachine</v>
+        <v>Scorpions</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-01</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Scorpions</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-01</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-01</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-01</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Holly Humberstone</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-01</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H102" t="str">
-        <v>Mae Muller</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L102" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G103" t="str">
-        <v>2:50</v>
+        <v>3:29</v>
       </c>
       <c r="H103" t="str">
-        <v>Zara Larsson</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L103" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Shape of a Woman</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G104" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H104" t="str">
-        <v>Lady Gaga</v>
+        <v>Madonna</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L104" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Bring Your Love</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>CONFESSIONS II</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G105" t="str">
-        <v>3:36</v>
+        <v>2:43</v>
       </c>
       <c r="H105" t="str">
-        <v>Madonna</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L105" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Horses and Divorces</v>
+        <v>Staying Still</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G106" t="str">
-        <v>2:43</v>
+        <v>4:28</v>
       </c>
       <c r="H106" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L106" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Staying Still</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>4:28</v>
+        <v>3:07</v>
       </c>
       <c r="H107" t="str">
-        <v>Noah Kahan</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L107" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>MUTT</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:07</v>
+        <v>1:59</v>
       </c>
       <c r="H108" t="str">
-        <v>Alex Warren</v>
+        <v>NAV</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L108" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>MUTT</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>MUTT - Single</v>
+        <v>Victory</v>
       </c>
       <c r="G109" t="str">
-        <v>1:59</v>
+        <v>3:27</v>
       </c>
       <c r="H109" t="str">
-        <v>NAV</v>
+        <v>Madeon</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L109" t="str">
-        <v>MUTT - NAV</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>Lioness</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Victory</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G110" t="str">
-        <v>3:27</v>
+        <v>3:32</v>
       </c>
       <c r="H110" t="str">
-        <v>Madeon</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L110" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lioness</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:32</v>
+        <v>2:19</v>
       </c>
       <c r="H111" t="str">
-        <v>Maya Hawke</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L111" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>IT'S OK</v>
+        <v>Promise?</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:19</v>
+        <v>3:12</v>
       </c>
       <c r="H112" t="str">
-        <v>Bryson Tiller</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L112" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Promise?</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Promise? - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G113" t="str">
-        <v>3:12</v>
+        <v>2:32</v>
       </c>
       <c r="H113" t="str">
-        <v>Bella Kay</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L113" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Cool Buzz</v>
+        <v>Material Lover</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Be Sweet To Me</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G114" t="str">
-        <v>2:32</v>
+        <v>2:58</v>
       </c>
       <c r="H114" t="str">
-        <v>Violet Grohl</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L114" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Material Lover</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>BROWN</v>
       </c>
       <c r="G115" t="str">
-        <v>2:58</v>
+        <v>4:26</v>
       </c>
       <c r="H115" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L115" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Echo</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>BROWN</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:26</v>
+        <v>2:15</v>
       </c>
       <c r="H116" t="str">
-        <v>Chris Brown</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L116" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Echo</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G117" t="str">
-        <v>2:15</v>
+        <v>3:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Daddy Yankee</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L117" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Cry Baby</v>
+        <v>CORSA</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>2:55</v>
       </c>
       <c r="H118" t="str">
-        <v>Vince Staples</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L118" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Ricky Bobby</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>CORSA</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:55</v>
+        <v>5:35</v>
       </c>
       <c r="H119" t="str">
-        <v>Eladio Carrión</v>
+        <v>Maisak</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L119" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>5:35</v>
+        <v>3:27</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisak</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L120" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Don't Worry Baby</v>
+        <v>BITCH</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>BITCH</v>
       </c>
       <c r="G121" t="str">
-        <v>3:27</v>
+        <v>2:42</v>
       </c>
       <c r="H121" t="str">
-        <v>Dom Dolla</v>
+        <v>Lizzo</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L121" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>BITCH</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BITCH</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G122" t="str">
-        <v>2:42</v>
+        <v>2:27</v>
       </c>
       <c r="H122" t="str">
-        <v>Lizzo</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L122" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Just Wanna Cry</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:27</v>
+        <v>3:09</v>
       </c>
       <c r="H123" t="str">
-        <v>Meghan Trainor</v>
+        <v>Halsey</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L123" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Carry the Weight</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>3:09</v>
+        <v>2:44</v>
       </c>
       <c r="H124" t="str">
-        <v>Halsey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L124" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PROSTITUTE</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G125" t="str">
-        <v>2:44</v>
+        <v>3:54</v>
       </c>
       <c r="H125" t="str">
-        <v>Labrinth</v>
+        <v>Bleachers</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L125" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>i'm not joking</v>
+        <v>Ruca</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>everyone for ten minutes</v>
+        <v>MUDA</v>
       </c>
       <c r="G126" t="str">
-        <v>3:54</v>
+        <v>3:01</v>
       </c>
       <c r="H126" t="str">
-        <v>Bleachers</v>
+        <v>Carín León</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L126" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Ruca</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>MUDA</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:01</v>
+        <v>2:55</v>
       </c>
       <c r="H127" t="str">
-        <v>Carín León</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L127" t="str">
-        <v>Ruca - Carín León</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Make You Fight</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Make You Fight - Single</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>2:55</v>
+        <v>1:43</v>
       </c>
       <c r="H128" t="str">
-        <v>Chris Lake</v>
+        <v>North West</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L128" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>#N0rth4evr</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G129" t="str">
-        <v>1:43</v>
+        <v>3:09</v>
       </c>
       <c r="H129" t="str">
-        <v>North West</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L129" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>BOY IN RED</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:09</v>
+        <v>2:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L130" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>EA EA EA</v>
+        <v>Just A Man</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:42</v>
+        <v>2:19</v>
       </c>
       <c r="H131" t="str">
-        <v>Clave Especial</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L131" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Just A Man</v>
+        <v>The Observer</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Just A Man - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G132" t="str">
-        <v>2:19</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L132" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>The Observer</v>
+        <v>Heroine</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:50</v>
+        <v>2:35</v>
       </c>
       <c r="H133" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L133" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Heroine</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Heroine - Single</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G134" t="str">
-        <v>2:35</v>
+        <v>4:10</v>
       </c>
       <c r="H134" t="str">
-        <v>Maroon 5</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L134" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Do Me Right</v>
+        <v>It's Me</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>FANTASYLAND</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G135" t="str">
-        <v>4:10</v>
+        <v>2:18</v>
       </c>
       <c r="H135" t="str">
-        <v>MR. FANTASY</v>
+        <v>ILLIT</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L135" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>It's Me</v>
+        <v>the precipice</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>2:18</v>
+        <v>3:52</v>
       </c>
       <c r="H136" t="str">
-        <v>ILLIT</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L136" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>the precipice</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G137" t="str">
-        <v>3:52</v>
+        <v>2:58</v>
       </c>
       <c r="H137" t="str">
-        <v>Jessie Mazin</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L137" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hello Lonesome</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:58</v>
+        <v>2:21</v>
       </c>
       <c r="H138" t="str">
-        <v>Cody Johnson</v>
+        <v>BUNT.</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L138" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:21</v>
+        <v>5:54</v>
       </c>
       <c r="H139" t="str">
-        <v>BUNT.</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L139" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>5:54</v>
+        <v>2:49</v>
       </c>
       <c r="H140" t="str">
-        <v>Ludwig Göransson</v>
+        <v>Robyn</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L140" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Robyn</v>
+        <v>The-Dream</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L141" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Bring That Body</v>
+        <v>STAR</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Bring That Body - Single</v>
+        <v>STAR</v>
       </c>
       <c r="G142" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H142" t="str">
-        <v>The-Dream</v>
+        <v>Tombochio</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L142" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>STAR</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>STAR</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G143" t="str">
-        <v>2:49</v>
+        <v>3:37</v>
       </c>
       <c r="H143" t="str">
-        <v>Tombochio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L143" t="str">
-        <v>STAR - Tombochio</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>What’s A Little Rain</v>
+        <v>Evergreen</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Deep Blue</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G144" t="str">
-        <v>3:37</v>
+        <v>3:41</v>
       </c>
       <c r="H144" t="str">
-        <v>ERNEST</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L144" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Evergreen</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Victory Garden</v>
+        <v>Peaches!</v>
       </c>
       <c r="G145" t="str">
-        <v>3:41</v>
+        <v>3:43</v>
       </c>
       <c r="H145" t="str">
-        <v>Young the Giant</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L145" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>She Does It Right</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Peaches!</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G146" t="str">
-        <v>3:43</v>
+        <v>3:11</v>
       </c>
       <c r="H146" t="str">
-        <v>The Black Keys</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L146" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Punching the Flowers</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>I Built You A Tower</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G147" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H147" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L147" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>How Did You Know</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>flow state</v>
       </c>
       <c r="G148" t="str">
-        <v>3:16</v>
+        <v>4:00</v>
       </c>
       <c r="H148" t="str">
-        <v>Jon Pardi</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L148" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Summer Breeze</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>flow state</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G149" t="str">
-        <v>4:00</v>
+        <v>4:27</v>
       </c>
       <c r="H149" t="str">
-        <v>Keith Urban</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L149" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Sound of a Woman</v>
+        <v>My Life</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Sound of a Woman</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G150" t="str">
-        <v>4:27</v>
+        <v>3:31</v>
       </c>
       <c r="H150" t="str">
-        <v>Rita Wilson</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L150" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>My Life</v>
+        <v>Ribcage</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>BERNARR.</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H151" t="str">
-        <v>Durand Bernarr</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L151" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ribcage</v>
+        <v>i loved you then</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Ribcage - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G152" t="str">
-        <v>3:00</v>
+        <v>3:42</v>
       </c>
       <c r="H152" t="str">
-        <v>Bella Poarch</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L152" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>i loved you then</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G153" t="str">
-        <v>3:42</v>
+        <v>3:54</v>
       </c>
       <c r="H153" t="str">
-        <v>Alana Springsteen</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L153" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I'll Let You Finish</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Fire From The Hip</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G154" t="str">
-        <v>3:54</v>
+        <v>2:53</v>
       </c>
       <c r="H154" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L154" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>It Gets Me Through</v>
+        <v>The Author</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:53</v>
+        <v>4:36</v>
       </c>
       <c r="H155" t="str">
-        <v>Laura Marano</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L155" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>The Author</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>The Author - Single</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>4:36</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Brandon Lake</v>
+        <v>Trousdale</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L156" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>RUIN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>3:23</v>
       </c>
       <c r="H157" t="str">
-        <v>Trousdale</v>
+        <v>HEALTH</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L157" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>RUIN</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>ADDENDUM</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:23</v>
+        <v>2:39</v>
       </c>
       <c r="H158" t="str">
-        <v>HEALTH</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L158" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>I Know I Know</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>I Know I Know - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H159" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L159" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Drive All Night</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Drive All Night - Single</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:50</v>
+        <v>3:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L160" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G161" t="str">
-        <v>3:41</v>
+        <v>2:33</v>
       </c>
       <c r="H161" t="str">
-        <v>Jessie Reyez</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L161" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Boys In Blue</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Emotional Junglist</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:33</v>
+        <v>3:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Nia Archives</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L162" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Salma Hayek</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:43</v>
+        <v>3:02</v>
       </c>
       <c r="H163" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L163" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Stubborn Mouth</v>
+        <v>Hallucination</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>3:02</v>
+        <v>3:22</v>
       </c>
       <c r="H164" t="str">
-        <v>Girl Tones</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L164" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Hallucination</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:22</v>
+        <v>2:44</v>
       </c>
       <c r="H165" t="str">
-        <v>Isabel LaRosa</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L165" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>In Da Jungle</v>
+        <v>Fall Short</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G166" t="str">
         <v>2:44</v>
       </c>
       <c r="H166" t="str">
-        <v>BLOND:ISH</v>
+        <v>nyan</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L166" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fall Short</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Fall Short - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G167" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H167" t="str">
-        <v>nyan</v>
+        <v>Kneecap</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L167" t="str">
-        <v>Fall Short - nyan</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>1989</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>FENIAN</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:34</v>
+        <v>3:05</v>
       </c>
       <c r="H168" t="str">
-        <v>Kneecap</v>
+        <v>Nightly</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L168" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>1989</v>
+        <v>no more regrets</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>1989 - Single</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:05</v>
+        <v>2:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Nightly</v>
+        <v>almost monday</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L169" t="str">
-        <v>1989 - Nightly</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>no more regrets</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>no more regrets - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G170" t="str">
-        <v>2:58</v>
+        <v>3:16</v>
       </c>
       <c r="H170" t="str">
-        <v>almost monday</v>
+        <v>Melanie C</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L170" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Drum Machine</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Sweat</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:16</v>
+        <v>2:36</v>
       </c>
       <c r="H171" t="str">
-        <v>Melanie C</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L171" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>I'm Perfect</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>2:36</v>
+        <v>5:05</v>
       </c>
       <c r="H172" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L172" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>5:05</v>
+        <v>2:27</v>
       </c>
       <c r="H173" t="str">
-        <v>Anish Kumar</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L173" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Bitch You Weird</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>24</v>
       </c>
       <c r="G174" t="str">
-        <v>2:27</v>
+        <v>2:24</v>
       </c>
       <c r="H174" t="str">
-        <v>Real Boston Richey</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L174" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Blackbird Rising</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>24</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:24</v>
+        <v>3:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L175" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>usher in the spirit</v>
+        <v>Moonlight</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>Aaron Cole</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L176" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Moonlight</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Moonlight - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>2:17</v>
       </c>
       <c r="H177" t="str">
-        <v>Chelsea Plank</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L177" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Closure</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:17</v>
+        <v>2:27</v>
       </c>
       <c r="H178" t="str">
-        <v>Becky Hill</v>
+        <v>D.O.D</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L178" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Closure</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Closure - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H179" t="str">
-        <v>D.O.D</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L179" t="str">
-        <v>Closure - D.O.D</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>HOTS 4 U</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>2:20</v>
       </c>
       <c r="H180" t="str">
-        <v>Chris Lorenzo</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L180" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G181" t="str">
-        <v>2:20</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>ARIA VEGA</v>
+        <v>Curren$y</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L181" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The Coin Toss</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:46</v>
+        <v>3:25</v>
       </c>
       <c r="H182" t="str">
-        <v>Curren$y</v>
+        <v>Chxrry</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L182" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:25</v>
+        <v>3:02</v>
       </c>
       <c r="H183" t="str">
-        <v>Chxrry</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L183" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Perfect For Me</v>
+        <v>So…</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:02</v>
+        <v>3:16</v>
       </c>
       <c r="H184" t="str">
-        <v>Jamal Roberts</v>
+        <v>Ama</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L184" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>So…</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>So… - Single</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:16</v>
+        <v>3:01</v>
       </c>
       <c r="H185" t="str">
-        <v>Ama</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L185" t="str">
-        <v>So… - Ama</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>PASE Y PASE</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G186" t="str">
-        <v>3:01</v>
+        <v>4:13</v>
       </c>
       <c r="H186" t="str">
-        <v>Tito Double P</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L186" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:13</v>
+        <v>6:12</v>
       </c>
       <c r="H187" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L187" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Aljahalat</v>
+        <v>Puleza</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Aljahalat - Single</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G188" t="str">
-        <v>6:12</v>
+        <v>3:47</v>
       </c>
       <c r="H188" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L188" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Puleza</v>
+        <v>Bastards</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>People of the Moon</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>3:47</v>
+        <v>2:56</v>
       </c>
       <c r="H189" t="str">
-        <v>Nu Genea</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L189" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Bastards</v>
+        <v>Crutch</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Bunny - EP</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:56</v>
+        <v>3:31</v>
       </c>
       <c r="H190" t="str">
-        <v>People I’ve Met</v>
+        <v>Love Spells</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L190" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Crutch</v>
+        <v>Just A Man</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Crutch - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:31</v>
+        <v>2:38</v>
       </c>
       <c r="H191" t="str">
-        <v>Love Spells</v>
+        <v>MOIO</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L191" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Just A Man</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Just A Man - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:38</v>
+        <v>3:51</v>
       </c>
       <c r="H192" t="str">
-        <v>MOIO</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L192" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Take Care Of You</v>
+        <v>Love You More</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:51</v>
+        <v>2:48</v>
       </c>
       <c r="H193" t="str">
-        <v>Alina Baraz</v>
+        <v>Rudimental</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L193" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Love You More</v>
+        <v>Construct</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Love You More - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G194" t="str">
-        <v>2:48</v>
+        <v>3:57</v>
       </c>
       <c r="H194" t="str">
-        <v>Rudimental</v>
+        <v>Sevendust</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L194" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Construct</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>ONE</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G195" t="str">
-        <v>3:57</v>
+        <v>4:54</v>
       </c>
       <c r="H195" t="str">
-        <v>Sevendust</v>
+        <v>Venom</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L195" t="str">
-        <v>Construct - Sevendust</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>As Above So Below</v>
+        <v>Revenant</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Into Oblivion</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G196" t="str">
-        <v>4:54</v>
+        <v>3:31</v>
       </c>
       <c r="H196" t="str">
-        <v>Venom</v>
+        <v>Loathe</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L196" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Revenant</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>A Stranger To You</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:31</v>
+        <v>4:56</v>
       </c>
       <c r="H197" t="str">
-        <v>Loathe</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L197" t="str">
-        <v>Revenant - Loathe</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Power 4</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:56</v>
+        <v>1:40</v>
       </c>
       <c r="H198" t="str">
-        <v>Bear McCreary</v>
+        <v>slayr</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L198" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Power 4</v>
+        <v>Too Easy</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Power 4 - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>1:40</v>
+        <v>4:14</v>
       </c>
       <c r="H199" t="str">
-        <v>slayr</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L199" t="str">
-        <v>Power 4 - slayr</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Too Easy</v>
+        <v>If You Want It</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Too Easy - Single</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:14</v>
+        <v>3:56</v>
       </c>
       <c r="H200" t="str">
-        <v>tig3r lewis</v>
+        <v>ALAC</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L200" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>If You Want It</v>
+        <v>Shoplifting</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>If You Want It - Single</v>
+        <v>Theft World</v>
       </c>
       <c r="G201" t="str">
-        <v>3:56</v>
+        <v>3:02</v>
       </c>
       <c r="H201" t="str">
-        <v>ALAC</v>
+        <v>Lip Critic</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
       </c>
       <c r="L201" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Shoplifting - Lip Critic</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Shoplifting</v>
+        <v>Endlessly (feat. BEA1991)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-01</v>
@@ -8051,68 +8051,30 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Theft World</v>
+        <v>Fold</v>
       </c>
       <c r="G202" t="str">
-        <v>3:02</v>
+        <v>5:57</v>
       </c>
       <c r="H202" t="str">
-        <v>Lip Critic</v>
+        <v>Jump Source</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
       <c r="L202" t="str">
-        <v>Shoplifting - Lip Critic</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Endlessly (feat. BEA1991)</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Fold</v>
-      </c>
-      <c r="G203" t="str">
-        <v>5:57</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Jump Source</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
-      </c>
-      <c r="L203" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
         <v>4 days ago</v>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY - Lady Gaga and Doechii</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E202" t="str">
         <v/>

--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>אוליביה רודריגו Drop Dead</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>2026-05-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%a8%d7%95%d7%93%d7%a8%d7%99%d7%92%d7%95-drop-dead/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-02</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>“לילה אחד השתעממתי במיטה / ועקבתי אחריך באינטרנט,” שרה אוליביה רודריגו בסינגל הקאמבק שלה, שכובש כל פסגה במצעדי העולם. שירים חדים, אובססיביים ובלתי מתפשרים על רומנטיקה – תמיד עם מודעות עצמית לעוצמה שלהם, או קריצה לאופן שבו בנות מאוהבות מתויגות</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Keith Urban</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>אוליביה רודריגו Drop Dead</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-02</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Danna</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-02</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Armik</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-02</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Europe</v>
+        <v>Jessie J</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-02</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Foo Fighters</v>
+        <v>The Takes</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-02</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>The Offspring</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-02</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Muse</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-02</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The Beaches</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-02</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Shaboozey</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-02</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Scorpions</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-02</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Meghan Trainor</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-02</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-02</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Letdown.</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-02</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-02</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Icona Pop</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-02</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Michael Jackson</v>
+        <v>ERNEST</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-02</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>The All-American Rejects</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-02</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Ringo Starr</v>
+        <v>Halsey</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-02</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-02</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Demi Lovato</v>
+        <v>Halsey</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-02</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-02</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-02</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Ella Langley</v>
+        <v>almost monday</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-02</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Meghan Trainor</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-02</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lukas Graham</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-02</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Foo Fighters</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-02</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>RUEL</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-02</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Haiden Henderson</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-02</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Conan Gray</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-02</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Foo Fighters</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-02</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ringo Starr</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-02</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bublé</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-02</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Malcolm Todd</v>
+        <v>Dons</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-02</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Sam Feldt</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-02</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Niall Horan</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-02</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Laufey</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-02</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Duran Duran</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-02</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Freya Skye</v>
+        <v>Danna</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-02</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Armik</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-02</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Danna</v>
+        <v>Europe</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-02</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-02</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-02</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Cannons</v>
+        <v>Muse</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-02</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Beck</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-02</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-02</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Scorpions</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-02</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Digster Pop Music</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-02</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Beck</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-02</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The All-American Rejects</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-02</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Armin van Buuren</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-02</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Demi Lovato</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-02</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Madonna</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-02</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Freya Ridings</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-02</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Celine Dion</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-02</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Peter Gabriel</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-02</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-02</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-02</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-02</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>ERNEST</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-02</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-02</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dean Lewis</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-02</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-02</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kip Moore</v>
+        <v>RUEL</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-02</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-02</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Ben Gallaher</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-02</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-02</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Johnny Orlando</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-02</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Tyla</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-02</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-02</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Lana Del Rey</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-02</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Loreen</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-02</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-02</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tenille Townes</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-02</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-02</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Danna</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-02</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>OneRepublic</v>
+        <v>Danna</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-02</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Revivalists</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-02</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>James Smith</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-02</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cannons</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-02</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ava Max</v>
+        <v>Beck</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-02</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>John Summit</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-02</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Ava Max</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-02</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Danna</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-02</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Conan Gray</v>
+        <v>Beck</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-02</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>TemplesOfficial</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-02</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Laufey</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-02</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>bleachers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-02</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Madonna</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-02</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>LANY</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-02</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-02</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-02</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-02</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Cinematic Official Video) - Kygo and carter faith</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-02</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>florencemachine</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-02</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Scorpions</v>
+        <v>ERNEST</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-02</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Holly Humberstone</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-02</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>HAUSER</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-02</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Holly Humberstone</v>
+        <v>Bella White</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-02</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-02</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Mae Muller</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Zara Larsson</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shape of a Woman</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G103" t="str">
-        <v>3:29</v>
+        <v>2:50</v>
       </c>
       <c r="H103" t="str">
-        <v>Lady Gaga</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L103" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Bring Your Love</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>CONFESSIONS II</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G104" t="str">
-        <v>3:36</v>
+        <v>3:29</v>
       </c>
       <c r="H104" t="str">
-        <v>Madonna</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L104" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Horses and Divorces</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Middle of Nowhere</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G105" t="str">
-        <v>2:43</v>
+        <v>3:36</v>
       </c>
       <c r="H105" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Madonna</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L105" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Staying Still</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G106" t="str">
-        <v>4:28</v>
+        <v>2:43</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L106" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>Staying Still</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G107" t="str">
-        <v>3:07</v>
+        <v>4:28</v>
       </c>
       <c r="H107" t="str">
-        <v>Alex Warren</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L107" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>MUTT</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>MUTT - Single</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>1:59</v>
+        <v>3:07</v>
       </c>
       <c r="H108" t="str">
-        <v>NAV</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L108" t="str">
-        <v>MUTT - NAV</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>MUTT</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Victory</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:27</v>
+        <v>1:59</v>
       </c>
       <c r="H109" t="str">
-        <v>Madeon</v>
+        <v>NAV</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L109" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Lioness</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Victory</v>
       </c>
       <c r="G110" t="str">
-        <v>3:32</v>
+        <v>3:27</v>
       </c>
       <c r="H110" t="str">
-        <v>Maya Hawke</v>
+        <v>Madeon</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L110" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>IT'S OK</v>
+        <v>Lioness</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>IT'S OK - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G111" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H111" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L111" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Promise?</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Promise? - Single</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:12</v>
+        <v>2:19</v>
       </c>
       <c r="H112" t="str">
-        <v>Bella Kay</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L112" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Cool Buzz</v>
+        <v>Promise?</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:32</v>
+        <v>3:12</v>
       </c>
       <c r="H113" t="str">
-        <v>Violet Grohl</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L113" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Material Lover</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G114" t="str">
-        <v>2:58</v>
+        <v>2:32</v>
       </c>
       <c r="H114" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L114" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Material Lover</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>BROWN</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G115" t="str">
-        <v>4:26</v>
+        <v>2:58</v>
       </c>
       <c r="H115" t="str">
-        <v>Chris Brown</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L115" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Echo</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>BROWN</v>
       </c>
       <c r="G116" t="str">
-        <v>2:15</v>
+        <v>4:26</v>
       </c>
       <c r="H116" t="str">
-        <v>Daddy Yankee</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L116" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Echo</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Cry Baby</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:52</v>
+        <v>2:15</v>
       </c>
       <c r="H117" t="str">
-        <v>Vince Staples</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L117" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Ricky Bobby</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>CORSA</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G118" t="str">
-        <v>2:55</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Eladio Carrión</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L118" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>CORSA</v>
       </c>
       <c r="G119" t="str">
-        <v>5:35</v>
+        <v>2:55</v>
       </c>
       <c r="H119" t="str">
-        <v>Maisak</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L119" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Don't Worry Baby</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:27</v>
+        <v>5:35</v>
       </c>
       <c r="H120" t="str">
-        <v>Dom Dolla</v>
+        <v>Maisak</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L120" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:42</v>
+        <v>3:27</v>
       </c>
       <c r="H121" t="str">
-        <v>Lizzo</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L121" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Just Wanna Cry</v>
+        <v>BITCH</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>BITCH</v>
       </c>
       <c r="G122" t="str">
-        <v>2:27</v>
+        <v>2:42</v>
       </c>
       <c r="H122" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lizzo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L122" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Carry the Weight</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H123" t="str">
-        <v>Halsey</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L123" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PROSTITUTE</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:44</v>
+        <v>3:09</v>
       </c>
       <c r="H124" t="str">
-        <v>Labrinth</v>
+        <v>Halsey</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L124" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>i'm not joking</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>everyone for ten minutes</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G125" t="str">
-        <v>3:54</v>
+        <v>2:44</v>
       </c>
       <c r="H125" t="str">
-        <v>Bleachers</v>
+        <v>Labrinth</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L125" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Ruca</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>MUDA</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G126" t="str">
-        <v>3:01</v>
+        <v>3:54</v>
       </c>
       <c r="H126" t="str">
-        <v>Carín León</v>
+        <v>Bleachers</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L126" t="str">
-        <v>Ruca - Carín León</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Make You Fight</v>
+        <v>Ruca</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Make You Fight - Single</v>
+        <v>MUDA</v>
       </c>
       <c r="G127" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H127" t="str">
-        <v>Chris Lake</v>
+        <v>Carín León</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L127" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>#N0rth4evr</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>1:43</v>
+        <v>2:55</v>
       </c>
       <c r="H128" t="str">
-        <v>North West</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L128" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOY IN RED</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G129" t="str">
-        <v>3:09</v>
+        <v>1:43</v>
       </c>
       <c r="H129" t="str">
-        <v>Isaiah Rashad</v>
+        <v>North West</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L129" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>EA EA EA</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G130" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H130" t="str">
-        <v>Clave Especial</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L130" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Just A Man</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Just A Man - Single</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>2:19</v>
+        <v>2:42</v>
       </c>
       <c r="H131" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L131" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>The Observer</v>
+        <v>Just A Man</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>2:19</v>
       </c>
       <c r="H132" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L132" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Heroine</v>
+        <v>The Observer</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heroine - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G133" t="str">
-        <v>2:35</v>
+        <v>2:50</v>
       </c>
       <c r="H133" t="str">
-        <v>Maroon 5</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L133" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Do Me Right</v>
+        <v>Heroine</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FANTASYLAND</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:10</v>
+        <v>2:35</v>
       </c>
       <c r="H134" t="str">
-        <v>MR. FANTASY</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L134" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>It's Me</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G135" t="str">
-        <v>2:18</v>
+        <v>4:10</v>
       </c>
       <c r="H135" t="str">
-        <v>ILLIT</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L135" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>the precipice</v>
+        <v>It's Me</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H136" t="str">
-        <v>Jessie Mazin</v>
+        <v>ILLIT</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L136" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Hello Lonesome</v>
+        <v>the precipice</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G137" t="str">
-        <v>2:58</v>
+        <v>3:52</v>
       </c>
       <c r="H137" t="str">
-        <v>Cody Johnson</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L137" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G138" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H138" t="str">
-        <v>BUNT.</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L138" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>5:54</v>
+        <v>2:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Ludwig Göransson</v>
+        <v>BUNT.</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L139" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:49</v>
+        <v>5:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Robyn</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L140" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Bring That Body</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bring That Body - Single</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H141" t="str">
-        <v>The-Dream</v>
+        <v>Robyn</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L141" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>STAR</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>STAR</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Tombochio</v>
+        <v>The-Dream</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L142" t="str">
-        <v>STAR - Tombochio</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>What’s A Little Rain</v>
+        <v>STAR</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Deep Blue</v>
+        <v>STAR</v>
       </c>
       <c r="G143" t="str">
-        <v>3:37</v>
+        <v>2:49</v>
       </c>
       <c r="H143" t="str">
-        <v>ERNEST</v>
+        <v>Tombochio</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L143" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Evergreen</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Victory Garden</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G144" t="str">
-        <v>3:41</v>
+        <v>3:37</v>
       </c>
       <c r="H144" t="str">
-        <v>Young the Giant</v>
+        <v>ERNEST</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L144" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>She Does It Right</v>
+        <v>Evergreen</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Peaches!</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G145" t="str">
-        <v>3:43</v>
+        <v>3:41</v>
       </c>
       <c r="H145" t="str">
-        <v>The Black Keys</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L145" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Punching the Flowers</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>I Built You A Tower</v>
+        <v>Peaches!</v>
       </c>
       <c r="G146" t="str">
-        <v>3:11</v>
+        <v>3:43</v>
       </c>
       <c r="H146" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L146" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>How Did You Know</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G147" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H147" t="str">
-        <v>Jon Pardi</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L147" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Summer Breeze</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>flow state</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G148" t="str">
-        <v>4:00</v>
+        <v>3:16</v>
       </c>
       <c r="H148" t="str">
-        <v>Keith Urban</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L148" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Sound of a Woman</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Sound of a Woman</v>
+        <v>flow state</v>
       </c>
       <c r="G149" t="str">
-        <v>4:27</v>
+        <v>4:00</v>
       </c>
       <c r="H149" t="str">
-        <v>Rita Wilson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L149" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>My Life</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>BERNARR.</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G150" t="str">
-        <v>3:31</v>
+        <v>4:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Durand Bernarr</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L150" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ribcage</v>
+        <v>My Life</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ribcage - Single</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G151" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H151" t="str">
-        <v>Bella Poarch</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L151" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>i loved you then</v>
+        <v>Ribcage</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:42</v>
+        <v>3:00</v>
       </c>
       <c r="H152" t="str">
-        <v>Alana Springsteen</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L152" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>I'll Let You Finish</v>
+        <v>i loved you then</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Fire From The Hip</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G153" t="str">
-        <v>3:54</v>
+        <v>3:42</v>
       </c>
       <c r="H153" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L153" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>It Gets Me Through</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G154" t="str">
-        <v>2:53</v>
+        <v>3:54</v>
       </c>
       <c r="H154" t="str">
-        <v>Laura Marano</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L154" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>The Author</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Author - Single</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G155" t="str">
-        <v>4:36</v>
+        <v>2:53</v>
       </c>
       <c r="H155" t="str">
-        <v>Brandon Lake</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L155" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>The Author</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>4:36</v>
       </c>
       <c r="H156" t="str">
-        <v>Trousdale</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L156" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>RUIN</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>ADDENDUM</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>HEALTH</v>
+        <v>Trousdale</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L157" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>I Know I Know</v>
+        <v>RUIN</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>I Know I Know - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G158" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H158" t="str">
-        <v>STELLA LEFTY</v>
+        <v>HEALTH</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L158" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Drive All Night</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Drive All Night - Single</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Wyatt Flores</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L159" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H160" t="str">
-        <v>Jessie Reyez</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L160" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Boys In Blue</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Emotional Junglist</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:33</v>
+        <v>3:41</v>
       </c>
       <c r="H161" t="str">
-        <v>Nia Archives</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L161" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Salma Hayek</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G162" t="str">
-        <v>3:43</v>
+        <v>2:33</v>
       </c>
       <c r="H162" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L162" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Stubborn Mouth</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:02</v>
+        <v>3:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Girl Tones</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L163" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Hallucination</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:22</v>
+        <v>3:02</v>
       </c>
       <c r="H164" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L164" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>In Da Jungle</v>
+        <v>Hallucination</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>2:44</v>
+        <v>3:22</v>
       </c>
       <c r="H165" t="str">
-        <v>BLOND:ISH</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L165" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Fall Short</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Fall Short - Single</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G166" t="str">
         <v>2:44</v>
       </c>
       <c r="H166" t="str">
-        <v>nyan</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L166" t="str">
-        <v>Fall Short - nyan</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>Fall Short</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>FENIAN</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H167" t="str">
-        <v>Kneecap</v>
+        <v>nyan</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L167" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>1989</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>1989 - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G168" t="str">
-        <v>3:05</v>
+        <v>3:34</v>
       </c>
       <c r="H168" t="str">
-        <v>Nightly</v>
+        <v>Kneecap</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L168" t="str">
-        <v>1989 - Nightly</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>no more regrets</v>
+        <v>1989</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>no more regrets - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H169" t="str">
-        <v>almost monday</v>
+        <v>Nightly</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L169" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drum Machine</v>
+        <v>no more regrets</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Sweat</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:16</v>
+        <v>2:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Melanie C</v>
+        <v>almost monday</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L170" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>I'm Perfect</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G171" t="str">
-        <v>2:36</v>
+        <v>3:16</v>
       </c>
       <c r="H171" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Melanie C</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L171" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>5:05</v>
+        <v>2:36</v>
       </c>
       <c r="H172" t="str">
-        <v>Anish Kumar</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L172" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Bitch You Weird</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>2:27</v>
+        <v>5:05</v>
       </c>
       <c r="H173" t="str">
-        <v>Real Boston Richey</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L173" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Blackbird Rising</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>24</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:24</v>
+        <v>2:27</v>
       </c>
       <c r="H174" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L174" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>usher in the spirit</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>24</v>
       </c>
       <c r="G175" t="str">
-        <v>3:00</v>
+        <v>2:24</v>
       </c>
       <c r="H175" t="str">
-        <v>Aaron Cole</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L175" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Moonlight</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Moonlight - Single</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>3:00</v>
       </c>
       <c r="H176" t="str">
-        <v>Chelsea Plank</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L176" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Moonlight</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:17</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>Becky Hill</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L177" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Closure</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Closure - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:27</v>
+        <v>2:17</v>
       </c>
       <c r="H178" t="str">
-        <v>D.O.D</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L178" t="str">
-        <v>Closure - D.O.D</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>HOTS 4 U</v>
+        <v>Closure</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H179" t="str">
-        <v>Chris Lorenzo</v>
+        <v>D.O.D</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L179" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:20</v>
+        <v>3:34</v>
       </c>
       <c r="H180" t="str">
-        <v>ARIA VEGA</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L180" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The Coin Toss</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>2:20</v>
       </c>
       <c r="H181" t="str">
-        <v>Curren$y</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L181" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G182" t="str">
-        <v>3:25</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Chxrry</v>
+        <v>Curren$y</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L182" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Perfect For Me</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:02</v>
+        <v>3:25</v>
       </c>
       <c r="H183" t="str">
-        <v>Jamal Roberts</v>
+        <v>Chxrry</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L183" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>So…</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>So… - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:16</v>
+        <v>3:02</v>
       </c>
       <c r="H184" t="str">
-        <v>Ama</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L184" t="str">
-        <v>So… - Ama</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>PASE Y PASE</v>
+        <v>So…</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:01</v>
+        <v>3:16</v>
       </c>
       <c r="H185" t="str">
-        <v>Tito Double P</v>
+        <v>Ama</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L185" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:13</v>
+        <v>3:01</v>
       </c>
       <c r="H186" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L186" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Aljahalat</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Aljahalat - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G187" t="str">
-        <v>6:12</v>
+        <v>4:13</v>
       </c>
       <c r="H187" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L187" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Puleza</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>People of the Moon</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:47</v>
+        <v>6:12</v>
       </c>
       <c r="H188" t="str">
-        <v>Nu Genea</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L188" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Bastards</v>
+        <v>Puleza</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Bunny - EP</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G189" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H189" t="str">
-        <v>People I’ve Met</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L189" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Crutch</v>
+        <v>Bastards</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Crutch - Single</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>3:31</v>
+        <v>2:56</v>
       </c>
       <c r="H190" t="str">
-        <v>Love Spells</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L190" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Just A Man</v>
+        <v>Crutch</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Just A Man - Single</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:38</v>
+        <v>3:31</v>
       </c>
       <c r="H191" t="str">
-        <v>MOIO</v>
+        <v>Love Spells</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L191" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Take Care Of You</v>
+        <v>Just A Man</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:51</v>
+        <v>2:38</v>
       </c>
       <c r="H192" t="str">
-        <v>Alina Baraz</v>
+        <v>MOIO</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L192" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Love You More</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Love You More - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:48</v>
+        <v>3:51</v>
       </c>
       <c r="H193" t="str">
-        <v>Rudimental</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L193" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Construct</v>
+        <v>Love You More</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>ONE</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:57</v>
+        <v>2:48</v>
       </c>
       <c r="H194" t="str">
-        <v>Sevendust</v>
+        <v>Rudimental</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L194" t="str">
-        <v>Construct - Sevendust</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>As Above So Below</v>
+        <v>Construct</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Into Oblivion</v>
+        <v>ONE</v>
       </c>
       <c r="G195" t="str">
-        <v>4:54</v>
+        <v>3:57</v>
       </c>
       <c r="H195" t="str">
-        <v>Venom</v>
+        <v>Sevendust</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L195" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Revenant</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>A Stranger To You</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G196" t="str">
-        <v>3:31</v>
+        <v>4:54</v>
       </c>
       <c r="H196" t="str">
-        <v>Loathe</v>
+        <v>Venom</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L196" t="str">
-        <v>Revenant - Loathe</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Revenant</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G197" t="str">
-        <v>4:56</v>
+        <v>3:31</v>
       </c>
       <c r="H197" t="str">
-        <v>Bear McCreary</v>
+        <v>Loathe</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L197" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Power 4</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-02</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Power 4 - Single</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>1:40</v>
+        <v>4:56</v>
       </c>
       <c r="H198" t="str">
-        <v>slayr</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L198" t="str">
-        <v>Power 4 - slayr</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Too Easy</v>
+        <v>Power 4</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-02</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Too Easy - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:14</v>
+        <v>1:40</v>
       </c>
       <c r="H199" t="str">
-        <v>tig3r lewis</v>
+        <v>slayr</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L199" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>If You Want It</v>
+        <v>Too Easy</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-02</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>If You Want It - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:56</v>
+        <v>4:14</v>
       </c>
       <c r="H200" t="str">
-        <v>ALAC</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L200" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Shoplifting</v>
+        <v>If You Want It</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-02</v>
@@ -8013,68 +8013,106 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Theft World</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:02</v>
+        <v>3:56</v>
       </c>
       <c r="H201" t="str">
-        <v>Lip Critic</v>
+        <v>ALAC</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L201" t="str">
-        <v>Shoplifting - Lip Critic</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Shoplifting</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Theft World</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Lip Critic</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Shoplifting - Lip Critic</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
         <v>Endlessly (feat. BEA1991)</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-05-02</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D203" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
         <v>Fold</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G203" t="str">
         <v>5:57</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H203" t="str">
         <v>Jump Source</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
         <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K203" t="str">
         <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L203" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אוליביה רודריגו Drop Dead</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-02</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%a8%d7%95%d7%93%d7%a8%d7%99%d7%92%d7%95-drop-dead/</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-02</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“לילה אחד השתעממתי במיטה / ועקבתי אחריך באינטרנט,” שרה אוליביה רודריגו בסינגל הקאמבק שלה, שכובש כל פסגה במצעדי העולם. שירים חדים, אובססיביים ובלתי מתפשרים על רומנטיקה – תמיד עם מודעות עצמית לעוצמה שלהם, או קריצה לאופן שבו בנות מאוהבות מתויגות</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אוליביה רודריגו Drop Dead</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-02</v>
@@ -495,7 +495,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-02</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Rick Astley</v>
+        <v>Jessie J</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-02</v>
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Jessie J</v>
+        <v>The Takes</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B6" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-02</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>The Takes</v>
+        <v>The Offspring</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-02</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>The Offspring</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-02</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Beaches</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-02</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Beaches</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-02</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>The Kiffness</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-02</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Dennis Lloyd</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-02</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Anna Graves</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-02</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Brandon Lake</v>
+        <v>Letdown.</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-02</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Letdown.</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-02</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Maroon 5</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-02</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Olivia O'Brien</v>
+        <v>ERNEST</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-02</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>ERNEST</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-02</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Halsey</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-02</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Halsey</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-02</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Zara Larsson</v>
+        <v>Halsey</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B21" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-02</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Halsey</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-02</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Bishop Briggs</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B23" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-02</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Louis Tomlinson</v>
+        <v>almost monday</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-02</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>almost monday</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-02</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-02</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-02</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-02</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Zara Larsson</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-02</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Jordana Bryant</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-02</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Leanna Crawford</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B31" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-02</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Girl Tones</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-02</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Tauren Wells</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B33" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-02</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Matthew Ifield</v>
+        <v>Dons</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-02</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Dons</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-02</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-02</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Maya Hawke</v>
+        <v>Laufey</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-02</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Laufey</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-02</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Keith Urban</v>
+        <v>Danna</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-02</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Danna</v>
+        <v>Armik</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-02</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Armik</v>
+        <v>Europe</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-02</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Europe</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-02</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Foo Fighters</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-02</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Muse</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-02</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Muse</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-02</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-02</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Shaboozey</v>
+        <v>Scorpions</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-02</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Scorpions</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-02</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-02</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-02</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-02</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-02</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Icona Pop</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-02</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Michael Jackson</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-02</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>The All-American Rejects</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-02</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Ringo Starr</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-02</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-02</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Demi Lovato</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-02</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Dean Lewis</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-02</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Matt Hansen</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-02</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Ella Langley</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-02</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-02</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Lukas Graham</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-02</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Foo Fighters</v>
+        <v>RUEL</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-02</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>RUEL</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-02</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Haiden Henderson</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-02</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Conan Gray</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-02</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-02</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Ringo Starr</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-02</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Michael Bublé</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-02</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Malcolm Todd</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-02</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Sam Feldt</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-02</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Niall Horan</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-02</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-02</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Duran Duran</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-02</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Freya Skye</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-02</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Danna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-02</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Danna</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-02</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-02</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cannons</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-02</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Cannons</v>
+        <v>Beck</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-02</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Beck</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-02</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-02</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-02</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Digster Pop Music</v>
+        <v>Beck</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-02</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Beck</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-02</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The All-American Rejects</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-02</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-02</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Demi Lovato</v>
+        <v>Madonna</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-02</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Madonna</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-02</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Freya Ridings</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-02</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Celine Dion</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-02</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Peter Gabriel</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-02</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-02</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Jessie Ware</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-02</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>The Kid LAROI.</v>
+        <v>ERNEST</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-02</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>ERNEST</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-02</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-02</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Dean Lewis</v>
+        <v>Bella White</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-02</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Bella White</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-02</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Kip Moore</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-02</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H102" t="str">
-        <v>Ben Gallaher</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L102" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G103" t="str">
-        <v>2:50</v>
+        <v>3:29</v>
       </c>
       <c r="H103" t="str">
-        <v>Zara Larsson</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L103" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Shape of a Woman</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G104" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H104" t="str">
-        <v>Lady Gaga</v>
+        <v>Madonna</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L104" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Bring Your Love</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>CONFESSIONS II</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G105" t="str">
-        <v>3:36</v>
+        <v>2:43</v>
       </c>
       <c r="H105" t="str">
-        <v>Madonna</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L105" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Horses and Divorces</v>
+        <v>Staying Still</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G106" t="str">
-        <v>2:43</v>
+        <v>4:28</v>
       </c>
       <c r="H106" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L106" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Staying Still</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>4:28</v>
+        <v>3:07</v>
       </c>
       <c r="H107" t="str">
-        <v>Noah Kahan</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L107" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>MUTT</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:07</v>
+        <v>1:59</v>
       </c>
       <c r="H108" t="str">
-        <v>Alex Warren</v>
+        <v>NAV</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L108" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>MUTT</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>MUTT - Single</v>
+        <v>Victory</v>
       </c>
       <c r="G109" t="str">
-        <v>1:59</v>
+        <v>3:27</v>
       </c>
       <c r="H109" t="str">
-        <v>NAV</v>
+        <v>Madeon</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L109" t="str">
-        <v>MUTT - NAV</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>Lioness</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Victory</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G110" t="str">
-        <v>3:27</v>
+        <v>3:32</v>
       </c>
       <c r="H110" t="str">
-        <v>Madeon</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L110" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lioness</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:32</v>
+        <v>2:19</v>
       </c>
       <c r="H111" t="str">
-        <v>Maya Hawke</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L111" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>IT'S OK</v>
+        <v>Promise?</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:19</v>
+        <v>3:12</v>
       </c>
       <c r="H112" t="str">
-        <v>Bryson Tiller</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L112" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Promise?</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Promise? - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G113" t="str">
-        <v>3:12</v>
+        <v>2:32</v>
       </c>
       <c r="H113" t="str">
-        <v>Bella Kay</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L113" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Cool Buzz</v>
+        <v>Material Lover</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Be Sweet To Me</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G114" t="str">
-        <v>2:32</v>
+        <v>2:58</v>
       </c>
       <c r="H114" t="str">
-        <v>Violet Grohl</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L114" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Material Lover</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>BROWN</v>
       </c>
       <c r="G115" t="str">
-        <v>2:58</v>
+        <v>4:26</v>
       </c>
       <c r="H115" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L115" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Echo</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>BROWN</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:26</v>
+        <v>2:15</v>
       </c>
       <c r="H116" t="str">
-        <v>Chris Brown</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L116" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Echo</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G117" t="str">
-        <v>2:15</v>
+        <v>3:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Daddy Yankee</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L117" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Cry Baby</v>
+        <v>CORSA</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>2:55</v>
       </c>
       <c r="H118" t="str">
-        <v>Vince Staples</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L118" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Ricky Bobby</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>CORSA</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:55</v>
+        <v>5:35</v>
       </c>
       <c r="H119" t="str">
-        <v>Eladio Carrión</v>
+        <v>Maisak</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L119" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>5:35</v>
+        <v>3:27</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisak</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L120" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Don't Worry Baby</v>
+        <v>BITCH</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>BITCH</v>
       </c>
       <c r="G121" t="str">
-        <v>3:27</v>
+        <v>2:42</v>
       </c>
       <c r="H121" t="str">
-        <v>Dom Dolla</v>
+        <v>Lizzo</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L121" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>BITCH</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BITCH</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G122" t="str">
-        <v>2:42</v>
+        <v>2:27</v>
       </c>
       <c r="H122" t="str">
-        <v>Lizzo</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L122" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Just Wanna Cry</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:27</v>
+        <v>3:09</v>
       </c>
       <c r="H123" t="str">
-        <v>Meghan Trainor</v>
+        <v>Halsey</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L123" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Carry the Weight</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>3:09</v>
+        <v>2:44</v>
       </c>
       <c r="H124" t="str">
-        <v>Halsey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L124" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PROSTITUTE</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G125" t="str">
-        <v>2:44</v>
+        <v>3:54</v>
       </c>
       <c r="H125" t="str">
-        <v>Labrinth</v>
+        <v>Bleachers</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L125" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>i'm not joking</v>
+        <v>Ruca</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>everyone for ten minutes</v>
+        <v>MUDA</v>
       </c>
       <c r="G126" t="str">
-        <v>3:54</v>
+        <v>3:01</v>
       </c>
       <c r="H126" t="str">
-        <v>Bleachers</v>
+        <v>Carín León</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L126" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Ruca</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>MUDA</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:01</v>
+        <v>2:55</v>
       </c>
       <c r="H127" t="str">
-        <v>Carín León</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L127" t="str">
-        <v>Ruca - Carín León</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Make You Fight</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Make You Fight - Single</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>2:55</v>
+        <v>1:43</v>
       </c>
       <c r="H128" t="str">
-        <v>Chris Lake</v>
+        <v>North West</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L128" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>#N0rth4evr</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G129" t="str">
-        <v>1:43</v>
+        <v>3:09</v>
       </c>
       <c r="H129" t="str">
-        <v>North West</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L129" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>BOY IN RED</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:09</v>
+        <v>2:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L130" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>EA EA EA</v>
+        <v>Just A Man</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:42</v>
+        <v>2:19</v>
       </c>
       <c r="H131" t="str">
-        <v>Clave Especial</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L131" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Just A Man</v>
+        <v>The Observer</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Just A Man - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G132" t="str">
-        <v>2:19</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L132" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>The Observer</v>
+        <v>Heroine</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:50</v>
+        <v>2:35</v>
       </c>
       <c r="H133" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L133" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Heroine</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Heroine - Single</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G134" t="str">
-        <v>2:35</v>
+        <v>4:10</v>
       </c>
       <c r="H134" t="str">
-        <v>Maroon 5</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L134" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Do Me Right</v>
+        <v>It's Me</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>FANTASYLAND</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G135" t="str">
-        <v>4:10</v>
+        <v>2:18</v>
       </c>
       <c r="H135" t="str">
-        <v>MR. FANTASY</v>
+        <v>ILLIT</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L135" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>It's Me</v>
+        <v>the precipice</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>2:18</v>
+        <v>3:52</v>
       </c>
       <c r="H136" t="str">
-        <v>ILLIT</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L136" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>the precipice</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G137" t="str">
-        <v>3:52</v>
+        <v>2:58</v>
       </c>
       <c r="H137" t="str">
-        <v>Jessie Mazin</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L137" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hello Lonesome</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:58</v>
+        <v>2:21</v>
       </c>
       <c r="H138" t="str">
-        <v>Cody Johnson</v>
+        <v>BUNT.</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L138" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:21</v>
+        <v>5:54</v>
       </c>
       <c r="H139" t="str">
-        <v>BUNT.</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L139" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>5:54</v>
+        <v>2:49</v>
       </c>
       <c r="H140" t="str">
-        <v>Ludwig Göransson</v>
+        <v>Robyn</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L140" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Robyn</v>
+        <v>The-Dream</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L141" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Bring That Body</v>
+        <v>STAR</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Bring That Body - Single</v>
+        <v>STAR</v>
       </c>
       <c r="G142" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H142" t="str">
-        <v>The-Dream</v>
+        <v>Tombochio</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L142" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>STAR</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>STAR</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G143" t="str">
-        <v>2:49</v>
+        <v>3:37</v>
       </c>
       <c r="H143" t="str">
-        <v>Tombochio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L143" t="str">
-        <v>STAR - Tombochio</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>What’s A Little Rain</v>
+        <v>Evergreen</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Deep Blue</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G144" t="str">
-        <v>3:37</v>
+        <v>3:41</v>
       </c>
       <c r="H144" t="str">
-        <v>ERNEST</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L144" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Evergreen</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Victory Garden</v>
+        <v>Peaches!</v>
       </c>
       <c r="G145" t="str">
-        <v>3:41</v>
+        <v>3:43</v>
       </c>
       <c r="H145" t="str">
-        <v>Young the Giant</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L145" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>She Does It Right</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Peaches!</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G146" t="str">
-        <v>3:43</v>
+        <v>3:11</v>
       </c>
       <c r="H146" t="str">
-        <v>The Black Keys</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L146" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Punching the Flowers</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>I Built You A Tower</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G147" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H147" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L147" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>How Did You Know</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>flow state</v>
       </c>
       <c r="G148" t="str">
-        <v>3:16</v>
+        <v>4:00</v>
       </c>
       <c r="H148" t="str">
-        <v>Jon Pardi</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L148" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Summer Breeze</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>flow state</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G149" t="str">
-        <v>4:00</v>
+        <v>4:27</v>
       </c>
       <c r="H149" t="str">
-        <v>Keith Urban</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L149" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Sound of a Woman</v>
+        <v>My Life</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Sound of a Woman</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G150" t="str">
-        <v>4:27</v>
+        <v>3:31</v>
       </c>
       <c r="H150" t="str">
-        <v>Rita Wilson</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L150" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>My Life</v>
+        <v>Ribcage</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>BERNARR.</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H151" t="str">
-        <v>Durand Bernarr</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L151" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ribcage</v>
+        <v>i loved you then</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Ribcage - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G152" t="str">
-        <v>3:00</v>
+        <v>3:42</v>
       </c>
       <c r="H152" t="str">
-        <v>Bella Poarch</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L152" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>i loved you then</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G153" t="str">
-        <v>3:42</v>
+        <v>3:54</v>
       </c>
       <c r="H153" t="str">
-        <v>Alana Springsteen</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L153" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I'll Let You Finish</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Fire From The Hip</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G154" t="str">
-        <v>3:54</v>
+        <v>2:53</v>
       </c>
       <c r="H154" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L154" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>It Gets Me Through</v>
+        <v>The Author</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:53</v>
+        <v>4:36</v>
       </c>
       <c r="H155" t="str">
-        <v>Laura Marano</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L155" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>The Author</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>The Author - Single</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>4:36</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Brandon Lake</v>
+        <v>Trousdale</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L156" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>RUIN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>3:23</v>
       </c>
       <c r="H157" t="str">
-        <v>Trousdale</v>
+        <v>HEALTH</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L157" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>RUIN</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>ADDENDUM</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:23</v>
+        <v>2:39</v>
       </c>
       <c r="H158" t="str">
-        <v>HEALTH</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L158" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>I Know I Know</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>I Know I Know - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H159" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L159" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Drive All Night</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Drive All Night - Single</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:50</v>
+        <v>3:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L160" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G161" t="str">
-        <v>3:41</v>
+        <v>2:33</v>
       </c>
       <c r="H161" t="str">
-        <v>Jessie Reyez</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L161" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Boys In Blue</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Emotional Junglist</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:33</v>
+        <v>3:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Nia Archives</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L162" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Salma Hayek</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:43</v>
+        <v>3:02</v>
       </c>
       <c r="H163" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L163" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Stubborn Mouth</v>
+        <v>Hallucination</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>3:02</v>
+        <v>3:22</v>
       </c>
       <c r="H164" t="str">
-        <v>Girl Tones</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L164" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Hallucination</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:22</v>
+        <v>2:44</v>
       </c>
       <c r="H165" t="str">
-        <v>Isabel LaRosa</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L165" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>In Da Jungle</v>
+        <v>Fall Short</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G166" t="str">
         <v>2:44</v>
       </c>
       <c r="H166" t="str">
-        <v>BLOND:ISH</v>
+        <v>nyan</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L166" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fall Short</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Fall Short - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G167" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H167" t="str">
-        <v>nyan</v>
+        <v>Kneecap</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L167" t="str">
-        <v>Fall Short - nyan</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>1989</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>FENIAN</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:34</v>
+        <v>3:05</v>
       </c>
       <c r="H168" t="str">
-        <v>Kneecap</v>
+        <v>Nightly</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L168" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>1989</v>
+        <v>no more regrets</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>1989 - Single</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:05</v>
+        <v>2:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Nightly</v>
+        <v>almost monday</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L169" t="str">
-        <v>1989 - Nightly</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>no more regrets</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>no more regrets - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G170" t="str">
-        <v>2:58</v>
+        <v>3:16</v>
       </c>
       <c r="H170" t="str">
-        <v>almost monday</v>
+        <v>Melanie C</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L170" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Drum Machine</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Sweat</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:16</v>
+        <v>2:36</v>
       </c>
       <c r="H171" t="str">
-        <v>Melanie C</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L171" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>I'm Perfect</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>2:36</v>
+        <v>5:05</v>
       </c>
       <c r="H172" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L172" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>5:05</v>
+        <v>2:27</v>
       </c>
       <c r="H173" t="str">
-        <v>Anish Kumar</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L173" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Bitch You Weird</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>24</v>
       </c>
       <c r="G174" t="str">
-        <v>2:27</v>
+        <v>2:24</v>
       </c>
       <c r="H174" t="str">
-        <v>Real Boston Richey</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L174" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Blackbird Rising</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>24</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:24</v>
+        <v>3:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L175" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>usher in the spirit</v>
+        <v>Moonlight</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>Aaron Cole</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L176" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Moonlight</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Moonlight - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>2:17</v>
       </c>
       <c r="H177" t="str">
-        <v>Chelsea Plank</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L177" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Closure</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:17</v>
+        <v>2:27</v>
       </c>
       <c r="H178" t="str">
-        <v>Becky Hill</v>
+        <v>D.O.D</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L178" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Closure</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Closure - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H179" t="str">
-        <v>D.O.D</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L179" t="str">
-        <v>Closure - D.O.D</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>HOTS 4 U</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>2:20</v>
       </c>
       <c r="H180" t="str">
-        <v>Chris Lorenzo</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L180" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G181" t="str">
-        <v>2:20</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>ARIA VEGA</v>
+        <v>Curren$y</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L181" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The Coin Toss</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:46</v>
+        <v>3:25</v>
       </c>
       <c r="H182" t="str">
-        <v>Curren$y</v>
+        <v>Chxrry</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L182" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:25</v>
+        <v>3:02</v>
       </c>
       <c r="H183" t="str">
-        <v>Chxrry</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L183" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Perfect For Me</v>
+        <v>So…</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:02</v>
+        <v>3:16</v>
       </c>
       <c r="H184" t="str">
-        <v>Jamal Roberts</v>
+        <v>Ama</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L184" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>So…</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>So… - Single</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:16</v>
+        <v>3:01</v>
       </c>
       <c r="H185" t="str">
-        <v>Ama</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L185" t="str">
-        <v>So… - Ama</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>PASE Y PASE</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G186" t="str">
-        <v>3:01</v>
+        <v>4:13</v>
       </c>
       <c r="H186" t="str">
-        <v>Tito Double P</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L186" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:13</v>
+        <v>6:12</v>
       </c>
       <c r="H187" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L187" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Aljahalat</v>
+        <v>Puleza</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Aljahalat - Single</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G188" t="str">
-        <v>6:12</v>
+        <v>3:47</v>
       </c>
       <c r="H188" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L188" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Puleza</v>
+        <v>Bastards</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>People of the Moon</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>3:47</v>
+        <v>2:56</v>
       </c>
       <c r="H189" t="str">
-        <v>Nu Genea</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L189" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Bastards</v>
+        <v>Crutch</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Bunny - EP</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:56</v>
+        <v>3:31</v>
       </c>
       <c r="H190" t="str">
-        <v>People I’ve Met</v>
+        <v>Love Spells</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L190" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Crutch</v>
+        <v>Just A Man</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Crutch - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:31</v>
+        <v>2:38</v>
       </c>
       <c r="H191" t="str">
-        <v>Love Spells</v>
+        <v>MOIO</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L191" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Just A Man</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Just A Man - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:38</v>
+        <v>3:51</v>
       </c>
       <c r="H192" t="str">
-        <v>MOIO</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L192" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Take Care Of You</v>
+        <v>Love You More</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:51</v>
+        <v>2:48</v>
       </c>
       <c r="H193" t="str">
-        <v>Alina Baraz</v>
+        <v>Rudimental</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L193" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Love You More</v>
+        <v>Construct</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Love You More - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G194" t="str">
-        <v>2:48</v>
+        <v>3:57</v>
       </c>
       <c r="H194" t="str">
-        <v>Rudimental</v>
+        <v>Sevendust</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L194" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Construct</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>ONE</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G195" t="str">
-        <v>3:57</v>
+        <v>4:54</v>
       </c>
       <c r="H195" t="str">
-        <v>Sevendust</v>
+        <v>Venom</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L195" t="str">
-        <v>Construct - Sevendust</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>As Above So Below</v>
+        <v>Revenant</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Into Oblivion</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G196" t="str">
-        <v>4:54</v>
+        <v>3:31</v>
       </c>
       <c r="H196" t="str">
-        <v>Venom</v>
+        <v>Loathe</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L196" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Revenant</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>A Stranger To You</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:31</v>
+        <v>4:56</v>
       </c>
       <c r="H197" t="str">
-        <v>Loathe</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L197" t="str">
-        <v>Revenant - Loathe</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Power 4</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-02</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:56</v>
+        <v>1:40</v>
       </c>
       <c r="H198" t="str">
-        <v>Bear McCreary</v>
+        <v>slayr</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L198" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Power 4</v>
+        <v>Too Easy</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-02</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Power 4 - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>1:40</v>
+        <v>4:14</v>
       </c>
       <c r="H199" t="str">
-        <v>slayr</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L199" t="str">
-        <v>Power 4 - slayr</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Too Easy</v>
+        <v>If You Want It</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-02</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Too Easy - Single</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:14</v>
+        <v>3:56</v>
       </c>
       <c r="H200" t="str">
-        <v>tig3r lewis</v>
+        <v>ALAC</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L200" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>If You Want It</v>
+        <v>Shoplifting</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-02</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>If You Want It - Single</v>
+        <v>Theft World</v>
       </c>
       <c r="G201" t="str">
-        <v>3:56</v>
+        <v>3:02</v>
       </c>
       <c r="H201" t="str">
-        <v>ALAC</v>
+        <v>Lip Critic</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
       </c>
       <c r="L201" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Shoplifting - Lip Critic</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Shoplifting</v>
+        <v>Endlessly (feat. BEA1991)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-02</v>
@@ -8051,68 +8051,30 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Theft World</v>
+        <v>Fold</v>
       </c>
       <c r="G202" t="str">
-        <v>3:02</v>
+        <v>5:57</v>
       </c>
       <c r="H202" t="str">
-        <v>Lip Critic</v>
+        <v>Jump Source</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
       <c r="L202" t="str">
-        <v>Shoplifting - Lip Critic</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Endlessly (feat. BEA1991)</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-05-02</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Fold</v>
-      </c>
-      <c r="G203" t="str">
-        <v>5:57</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Jump Source</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
-      </c>
-      <c r="L203" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -1693,7 +1693,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>

--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -1579,7 +1579,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>

--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E202" t="str">
         <v/>

--- a/data/global/2026-05-week01/titles.xlsx
+++ b/data/global/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>אריאל דימנט – כשאתה</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%90%d7%9c-%d7%93%d7%99%d7%9e%d7%a0%d7%98-%d7%9b%d7%a9%d7%90%d7%aa%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-03</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>הקאבר ל־“כשאתה” בביצועה של אריאל דימנט מתוך המחזמר "בגלל הרוח" משירי שלומי שבת, הוא דוגמה יפה לאיך שיר אהבה מוכר יכול לקבל משמעות חדשה לגמרי כשהוא נכנס להקשר דרמטי. במקור, השיר של שלומי שבת בדואט עם בתו מנור שבת הוא</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>SIENNA SPIRO</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>אריאל דימנט – כשאתה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>הפטריקים – מלאך</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%9e%d7%9c%d7%90%d7%9a/</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-03</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>“מלאך” של מאיר גולדברג ודודי לוי בביצוע  הפטריקים (דודי לוי + אבטיפוס) הוא טקסט טעון בדימויים פואטיים שמערבבים בין פנטזיה קוסמית לבין חוויה מאוד אנושית של אובדן, זיכרון וזהות. המלאך מתואר כיצור חופש שמביט מלמעלה, אך החופש הזה מתגלה כאשליה:</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Rick Astley</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>הפטריקים – מלאך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-03</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Jessie J</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-03</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>The Takes</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-03</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>The Offspring</v>
+        <v>Jessie J</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-03</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Takes</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-03</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Beaches</v>
+        <v>The Offspring</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-03</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Kiffness</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-03</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Dennis Lloyd</v>
+        <v>The Beaches</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-03</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Anna Graves</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-03</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Brandon Lake</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-03</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Letdown.</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-03</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Maroon 5</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-03</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Letdown.</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-03</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>ERNEST</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-03</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-03</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Halsey</v>
+        <v>ERNEST</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-03</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Zara Larsson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-03</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-03</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Bishop Briggs</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-03</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Halsey</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-03</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>almost monday</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-03</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-03</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>almost monday</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-03</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-03</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Zara Larsson</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-03</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Jordana Bryant</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-03</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Leanna Crawford</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-03</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Girl Tones</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-03</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Tauren Wells</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-03</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Matthew Ifield</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-03</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Dons</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-03</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-03</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Maya Hawke</v>
+        <v>Dons</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-03</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Laufey</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-03</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Keith Urban</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-03</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Danna</v>
+        <v>Laufey</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-03</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Armik</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-03</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Europe</v>
+        <v>Danna</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-03</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Foo Fighters</v>
+        <v>Armik</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-03</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Europe</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-03</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Muse</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-03</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-03</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Shaboozey</v>
+        <v>Muse</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-03</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Scorpions</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-03</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Meghan Trainor</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-03</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Scorpions</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-03</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-03</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-03</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Icona Pop</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-03</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Michael Jackson</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-03</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>The All-American Rejects</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-03</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Ringo Starr</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-03</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-03</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Demi Lovato</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-03</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Dean Lewis</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-03</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Matt Hansen</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-03</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Ella Langley</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-03</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Meghan Trainor</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-03</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Lukas Graham</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-03</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Foo Fighters</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-03</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>RUEL</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-03</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Haiden Henderson</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-03</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Conan Gray</v>
+        <v>RUEL</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-03</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Foo Fighters</v>
+        <v>Haiden Henderson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-03</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Ringo Starr</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-03</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Michael Bublé</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-03</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Malcolm Todd</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-03</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Sam Feldt</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-03</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Niall Horan</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-03</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Sam Feldt</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-03</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Duran Duran</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-03</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Freya Skye</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-03</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-03</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Danna</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-03</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Purple Disco Machine</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-03</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Danna</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>DANNA - MOVIE STAR - Danna</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-03</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Cannons</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-03</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Beck</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-03</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Cannons</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-03</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Beck</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-03</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Digster Pop Music</v>
+        <v>Frank Walker and salem ilese</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-03</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Beck</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-03</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>The All-American Rejects</v>
+        <v>Digster Pop Music</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-03</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Armin van Buuren</v>
+        <v>Beck</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Beck - Ride Lonesome (Audio) - Beck</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-03</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Demi Lovato</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-03</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Madonna</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-03</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Freya Ridings</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-03</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Celine Dion</v>
+        <v>Madonna</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-03</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Peter Gabriel</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-03</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-03</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Jessie Ware</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-03</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-03</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>ERNEST</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-03</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-03</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Dean Lewis</v>
+        <v>ERNEST</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-03</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Bella White</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-03</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Kip Moore</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-03</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Bella White</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-03</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ben Gallaher</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-03</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>2w ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Zara Larsson</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shape of a Woman</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2w ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-03</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>2w ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:29</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Lady Gaga</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Bring Your Love</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-03</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>CONFESSIONS II</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G104" t="str">
-        <v>3:36</v>
+        <v>2:50</v>
       </c>
       <c r="H104" t="str">
-        <v>Madonna</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L104" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Horses and Divorces</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-03</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G105" t="str">
-        <v>2:43</v>
+        <v>3:29</v>
       </c>
       <c r="H105" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L105" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Staying Still</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-03</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G106" t="str">
-        <v>4:28</v>
+        <v>3:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Madonna</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L106" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-03</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G107" t="str">
-        <v>3:07</v>
+        <v>2:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Alex Warren</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L107" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>MUTT</v>
+        <v>Staying Still</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-03</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>MUTT - Single</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G108" t="str">
-        <v>1:59</v>
+        <v>4:28</v>
       </c>
       <c r="H108" t="str">
-        <v>NAV</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/albu